--- a/data/Database_Katalog_mi.do.ri.xlsx
+++ b/data/Database_Katalog_mi.do.ri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\mi.do.ri_Webstore_v2.3_Promo_GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71CCD4F-CB64-412D-8CAD-01E9F08862AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2539B2A-B17B-4332-9BC3-1B5D3E9FB0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4526" uniqueCount="1387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4565" uniqueCount="1390">
   <si>
     <t>ID_PRODUK</t>
   </si>
@@ -4194,6 +4194,15 @@
   </si>
   <si>
     <t>Ya</t>
+  </si>
+  <si>
+    <t>1 juli 2026</t>
+  </si>
+  <si>
+    <t>31 juli 2026</t>
+  </si>
+  <si>
+    <t>7.7 Sale</t>
   </si>
 </sst>
 </file>
@@ -4205,7 +4214,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -4220,6 +4229,10 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF07552E"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -4966,9 +4979,15 @@
       <c r="Z2" s="43">
         <v>60</v>
       </c>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="4"/>
+      <c r="AA2" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB2" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="3" spans="1:29" ht="28">
       <c r="A3" s="20" t="s">
@@ -5039,9 +5058,15 @@
       <c r="Z3" s="44">
         <v>60</v>
       </c>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="5"/>
+      <c r="AA3" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB3" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="20" t="s">
@@ -5112,9 +5137,15 @@
       <c r="Z4" s="44">
         <v>60</v>
       </c>
-      <c r="AA4" s="41"/>
-      <c r="AB4" s="41"/>
-      <c r="AC4" s="5"/>
+      <c r="AA4" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB4" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="20" t="s">
@@ -5185,9 +5216,15 @@
       <c r="Z5" s="44">
         <v>60</v>
       </c>
-      <c r="AA5" s="41"/>
-      <c r="AB5" s="41"/>
-      <c r="AC5" s="5"/>
+      <c r="AA5" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB5" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="6" spans="1:29">
       <c r="A6" s="20" t="s">
@@ -5256,9 +5293,15 @@
       <c r="Z6" s="44">
         <v>60</v>
       </c>
-      <c r="AA6" s="41"/>
-      <c r="AB6" s="41"/>
-      <c r="AC6" s="5"/>
+      <c r="AA6" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB6" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC6" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="20" t="s">
@@ -5327,9 +5370,15 @@
       <c r="Z7" s="44">
         <v>60</v>
       </c>
-      <c r="AA7" s="41"/>
-      <c r="AB7" s="41"/>
-      <c r="AC7" s="5"/>
+      <c r="AA7" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB7" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC7" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="20" t="s">
@@ -5400,9 +5449,15 @@
       <c r="Z8" s="44">
         <v>60</v>
       </c>
-      <c r="AA8" s="41"/>
-      <c r="AB8" s="41"/>
-      <c r="AC8" s="5"/>
+      <c r="AA8" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB8" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC8" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="20" t="s">
@@ -5473,9 +5528,15 @@
       <c r="Z9" s="44">
         <v>60</v>
       </c>
-      <c r="AA9" s="41"/>
-      <c r="AB9" s="41"/>
-      <c r="AC9" s="5"/>
+      <c r="AA9" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB9" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC9" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="20" t="s">
@@ -5546,9 +5607,15 @@
       <c r="Z10" s="44">
         <v>60</v>
       </c>
-      <c r="AA10" s="41"/>
-      <c r="AB10" s="41"/>
-      <c r="AC10" s="5"/>
+      <c r="AA10" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB10" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC10" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="20" t="s">
@@ -5617,9 +5684,15 @@
       <c r="Z11" s="44">
         <v>60</v>
       </c>
-      <c r="AA11" s="41"/>
-      <c r="AB11" s="41"/>
-      <c r="AC11" s="5"/>
+      <c r="AA11" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB11" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC11" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="12" spans="1:29">
       <c r="A12" s="20" t="s">
@@ -5688,9 +5761,15 @@
       <c r="Z12" s="44">
         <v>60</v>
       </c>
-      <c r="AA12" s="41"/>
-      <c r="AB12" s="41"/>
-      <c r="AC12" s="5"/>
+      <c r="AA12" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB12" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC12" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="13" spans="1:29">
       <c r="A13" s="20" t="s">
@@ -5759,9 +5838,15 @@
       <c r="Z13" s="44">
         <v>60</v>
       </c>
-      <c r="AA13" s="41"/>
-      <c r="AB13" s="41"/>
-      <c r="AC13" s="5"/>
+      <c r="AA13" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB13" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC13" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="14" spans="1:29">
       <c r="A14" s="20" t="s">
@@ -5830,9 +5915,15 @@
       <c r="Z14" s="44">
         <v>60</v>
       </c>
-      <c r="AA14" s="41"/>
-      <c r="AB14" s="41"/>
-      <c r="AC14" s="5"/>
+      <c r="AA14" s="40" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB14" s="40" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC14" s="4" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="15" spans="1:29">
       <c r="A15" s="20" t="s">
@@ -16676,6 +16767,7 @@
       <c r="AC167" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="Y2:AC167">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$Y2="Ya"</formula>

--- a/data/Database_Katalog_mi.do.ri.xlsx
+++ b/data/Database_Katalog_mi.do.ri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\mi.do.ri_Webstore_v2.3_Promo_GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2539B2A-B17B-4332-9BC3-1B5D3E9FB0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F971802-A5BE-4972-8762-AC921B371A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4565" uniqueCount="1390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4552" uniqueCount="1390">
   <si>
     <t>ID_PRODUK</t>
   </si>
@@ -4196,22 +4196,21 @@
     <t>Ya</t>
   </si>
   <si>
-    <t>1 juli 2026</t>
-  </si>
-  <si>
-    <t>31 juli 2026</t>
-  </si>
-  <si>
     <t>7.7 Sale</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>31/8/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;Rp&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="0&quot;%&quot;"/>
   </numFmts>
   <fonts count="4">
@@ -4510,12 +4509,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4976,17 +4975,17 @@
       <c r="Y2" s="37" t="s">
         <v>1386</v>
       </c>
-      <c r="Z2" s="43">
+      <c r="Z2" s="40">
         <v>60</v>
       </c>
-      <c r="AA2" s="40" t="s">
+      <c r="AA2" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB2" s="44" t="s">
+        <v>1389</v>
+      </c>
+      <c r="AC2" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB2" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="28">
@@ -5055,17 +5054,17 @@
       <c r="Y3" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z3" s="44">
+      <c r="Z3" s="41">
         <v>60</v>
       </c>
-      <c r="AA3" s="40" t="s">
+      <c r="AA3" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB3" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC3" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB3" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC3" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -5134,17 +5133,17 @@
       <c r="Y4" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z4" s="44">
+      <c r="Z4" s="41">
         <v>60</v>
       </c>
-      <c r="AA4" s="40" t="s">
+      <c r="AA4" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB4" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC4" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB4" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC4" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -5213,17 +5212,17 @@
       <c r="Y5" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z5" s="44">
+      <c r="Z5" s="41">
         <v>60</v>
       </c>
-      <c r="AA5" s="40" t="s">
+      <c r="AA5" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB5" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC5" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB5" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC5" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -5290,17 +5289,17 @@
       <c r="Y6" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z6" s="44">
+      <c r="Z6" s="41">
         <v>60</v>
       </c>
-      <c r="AA6" s="40" t="s">
+      <c r="AA6" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB6" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC6" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB6" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC6" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -5367,17 +5366,17 @@
       <c r="Y7" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z7" s="44">
+      <c r="Z7" s="41">
         <v>60</v>
       </c>
-      <c r="AA7" s="40" t="s">
+      <c r="AA7" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB7" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC7" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB7" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC7" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -5446,17 +5445,17 @@
       <c r="Y8" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z8" s="44">
+      <c r="Z8" s="41">
         <v>60</v>
       </c>
-      <c r="AA8" s="40" t="s">
+      <c r="AA8" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB8" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC8" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB8" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC8" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -5525,17 +5524,17 @@
       <c r="Y9" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z9" s="44">
+      <c r="Z9" s="41">
         <v>60</v>
       </c>
-      <c r="AA9" s="40" t="s">
+      <c r="AA9" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB9" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC9" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB9" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC9" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -5604,17 +5603,17 @@
       <c r="Y10" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z10" s="44">
+      <c r="Z10" s="41">
         <v>60</v>
       </c>
-      <c r="AA10" s="40" t="s">
+      <c r="AA10" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB10" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC10" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB10" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC10" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -5681,17 +5680,17 @@
       <c r="Y11" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z11" s="44">
+      <c r="Z11" s="41">
         <v>60</v>
       </c>
-      <c r="AA11" s="40" t="s">
+      <c r="AA11" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB11" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC11" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB11" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC11" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -5758,17 +5757,17 @@
       <c r="Y12" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z12" s="44">
+      <c r="Z12" s="41">
         <v>60</v>
       </c>
-      <c r="AA12" s="40" t="s">
+      <c r="AA12" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB12" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC12" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB12" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC12" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -5835,17 +5834,17 @@
       <c r="Y13" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z13" s="44">
+      <c r="Z13" s="41">
         <v>60</v>
       </c>
-      <c r="AA13" s="40" t="s">
+      <c r="AA13" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB13" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC13" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB13" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC13" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -5912,17 +5911,17 @@
       <c r="Y14" s="38" t="s">
         <v>1386</v>
       </c>
-      <c r="Z14" s="44">
+      <c r="Z14" s="41">
         <v>60</v>
       </c>
-      <c r="AA14" s="40" t="s">
+      <c r="AA14" s="44">
+        <v>46030</v>
+      </c>
+      <c r="AB14" s="44" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AC14" s="4" t="s">
         <v>1387</v>
-      </c>
-      <c r="AB14" s="40" t="s">
-        <v>1388</v>
-      </c>
-      <c r="AC14" s="4" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -5987,11 +5986,11 @@
       <c r="Y15" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z15" s="44">
+      <c r="Z15" s="41">
         <v>0</v>
       </c>
-      <c r="AA15" s="41"/>
-      <c r="AB15" s="41"/>
+      <c r="AA15" s="43"/>
+      <c r="AB15" s="43"/>
       <c r="AC15" s="5"/>
     </row>
     <row r="16" spans="1:29">
@@ -6060,11 +6059,11 @@
       <c r="Y16" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z16" s="44">
+      <c r="Z16" s="41">
         <v>0</v>
       </c>
-      <c r="AA16" s="41"/>
-      <c r="AB16" s="41"/>
+      <c r="AA16" s="43"/>
+      <c r="AB16" s="43"/>
       <c r="AC16" s="5"/>
     </row>
     <row r="17" spans="1:29">
@@ -6131,11 +6130,11 @@
       <c r="Y17" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z17" s="44">
+      <c r="Z17" s="41">
         <v>0</v>
       </c>
-      <c r="AA17" s="41"/>
-      <c r="AB17" s="41"/>
+      <c r="AA17" s="43"/>
+      <c r="AB17" s="43"/>
       <c r="AC17" s="5"/>
     </row>
     <row r="18" spans="1:29">
@@ -6202,11 +6201,11 @@
       <c r="Y18" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z18" s="44">
+      <c r="Z18" s="41">
         <v>0</v>
       </c>
-      <c r="AA18" s="41"/>
-      <c r="AB18" s="41"/>
+      <c r="AA18" s="43"/>
+      <c r="AB18" s="43"/>
       <c r="AC18" s="5"/>
     </row>
     <row r="19" spans="1:29">
@@ -6273,11 +6272,11 @@
       <c r="Y19" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z19" s="44">
+      <c r="Z19" s="41">
         <v>0</v>
       </c>
-      <c r="AA19" s="41"/>
-      <c r="AB19" s="41"/>
+      <c r="AA19" s="43"/>
+      <c r="AB19" s="43"/>
       <c r="AC19" s="5"/>
     </row>
     <row r="20" spans="1:29">
@@ -6344,11 +6343,11 @@
       <c r="Y20" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z20" s="44">
+      <c r="Z20" s="41">
         <v>0</v>
       </c>
-      <c r="AA20" s="41"/>
-      <c r="AB20" s="41"/>
+      <c r="AA20" s="43"/>
+      <c r="AB20" s="43"/>
       <c r="AC20" s="5"/>
     </row>
     <row r="21" spans="1:29">
@@ -6415,11 +6414,11 @@
       <c r="Y21" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z21" s="44">
+      <c r="Z21" s="41">
         <v>0</v>
       </c>
-      <c r="AA21" s="41"/>
-      <c r="AB21" s="41"/>
+      <c r="AA21" s="43"/>
+      <c r="AB21" s="43"/>
       <c r="AC21" s="5"/>
     </row>
     <row r="22" spans="1:29">
@@ -6486,11 +6485,11 @@
       <c r="Y22" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z22" s="44">
+      <c r="Z22" s="41">
         <v>0</v>
       </c>
-      <c r="AA22" s="41"/>
-      <c r="AB22" s="41"/>
+      <c r="AA22" s="43"/>
+      <c r="AB22" s="43"/>
       <c r="AC22" s="5"/>
     </row>
     <row r="23" spans="1:29">
@@ -6557,11 +6556,11 @@
       <c r="Y23" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z23" s="44">
+      <c r="Z23" s="41">
         <v>0</v>
       </c>
-      <c r="AA23" s="41"/>
-      <c r="AB23" s="41"/>
+      <c r="AA23" s="43"/>
+      <c r="AB23" s="43"/>
       <c r="AC23" s="5"/>
     </row>
     <row r="24" spans="1:29">
@@ -6628,11 +6627,11 @@
       <c r="Y24" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z24" s="44">
+      <c r="Z24" s="41">
         <v>0</v>
       </c>
-      <c r="AA24" s="41"/>
-      <c r="AB24" s="41"/>
+      <c r="AA24" s="43"/>
+      <c r="AB24" s="43"/>
       <c r="AC24" s="5"/>
     </row>
     <row r="25" spans="1:29">
@@ -6699,11 +6698,11 @@
       <c r="Y25" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z25" s="44">
+      <c r="Z25" s="41">
         <v>0</v>
       </c>
-      <c r="AA25" s="41"/>
-      <c r="AB25" s="41"/>
+      <c r="AA25" s="43"/>
+      <c r="AB25" s="43"/>
       <c r="AC25" s="5"/>
     </row>
     <row r="26" spans="1:29">
@@ -6772,11 +6771,11 @@
       <c r="Y26" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z26" s="44">
+      <c r="Z26" s="41">
         <v>0</v>
       </c>
-      <c r="AA26" s="41"/>
-      <c r="AB26" s="41"/>
+      <c r="AA26" s="43"/>
+      <c r="AB26" s="43"/>
       <c r="AC26" s="5"/>
     </row>
     <row r="27" spans="1:29">
@@ -6843,11 +6842,11 @@
       <c r="Y27" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z27" s="44">
+      <c r="Z27" s="41">
         <v>0</v>
       </c>
-      <c r="AA27" s="41"/>
-      <c r="AB27" s="41"/>
+      <c r="AA27" s="43"/>
+      <c r="AB27" s="43"/>
       <c r="AC27" s="5"/>
     </row>
     <row r="28" spans="1:29">
@@ -6914,11 +6913,11 @@
       <c r="Y28" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z28" s="44">
+      <c r="Z28" s="41">
         <v>0</v>
       </c>
-      <c r="AA28" s="41"/>
-      <c r="AB28" s="41"/>
+      <c r="AA28" s="43"/>
+      <c r="AB28" s="43"/>
       <c r="AC28" s="5"/>
     </row>
     <row r="29" spans="1:29">
@@ -6987,11 +6986,11 @@
       <c r="Y29" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z29" s="44">
+      <c r="Z29" s="41">
         <v>0</v>
       </c>
-      <c r="AA29" s="41"/>
-      <c r="AB29" s="41"/>
+      <c r="AA29" s="43"/>
+      <c r="AB29" s="43"/>
       <c r="AC29" s="5"/>
     </row>
     <row r="30" spans="1:29">
@@ -7058,11 +7057,11 @@
       <c r="Y30" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z30" s="44">
+      <c r="Z30" s="41">
         <v>0</v>
       </c>
-      <c r="AA30" s="41"/>
-      <c r="AB30" s="41"/>
+      <c r="AA30" s="43"/>
+      <c r="AB30" s="43"/>
       <c r="AC30" s="5"/>
     </row>
     <row r="31" spans="1:29">
@@ -7131,11 +7130,11 @@
       <c r="Y31" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z31" s="44">
+      <c r="Z31" s="41">
         <v>0</v>
       </c>
-      <c r="AA31" s="41"/>
-      <c r="AB31" s="41"/>
+      <c r="AA31" s="43"/>
+      <c r="AB31" s="43"/>
       <c r="AC31" s="5"/>
     </row>
     <row r="32" spans="1:29">
@@ -7202,11 +7201,11 @@
       <c r="Y32" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z32" s="44">
+      <c r="Z32" s="41">
         <v>0</v>
       </c>
-      <c r="AA32" s="41"/>
-      <c r="AB32" s="41"/>
+      <c r="AA32" s="43"/>
+      <c r="AB32" s="43"/>
       <c r="AC32" s="5"/>
     </row>
     <row r="33" spans="1:29">
@@ -7273,11 +7272,11 @@
       <c r="Y33" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z33" s="44">
+      <c r="Z33" s="41">
         <v>0</v>
       </c>
-      <c r="AA33" s="41"/>
-      <c r="AB33" s="41"/>
+      <c r="AA33" s="43"/>
+      <c r="AB33" s="43"/>
       <c r="AC33" s="5"/>
     </row>
     <row r="34" spans="1:29" ht="28">
@@ -7344,11 +7343,11 @@
       <c r="Y34" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z34" s="44">
+      <c r="Z34" s="41">
         <v>0</v>
       </c>
-      <c r="AA34" s="41"/>
-      <c r="AB34" s="41"/>
+      <c r="AA34" s="43"/>
+      <c r="AB34" s="43"/>
       <c r="AC34" s="5"/>
     </row>
     <row r="35" spans="1:29">
@@ -7415,11 +7414,11 @@
       <c r="Y35" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z35" s="44">
+      <c r="Z35" s="41">
         <v>0</v>
       </c>
-      <c r="AA35" s="41"/>
-      <c r="AB35" s="41"/>
+      <c r="AA35" s="43"/>
+      <c r="AB35" s="43"/>
       <c r="AC35" s="5"/>
     </row>
     <row r="36" spans="1:29">
@@ -7486,11 +7485,11 @@
       <c r="Y36" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z36" s="44">
+      <c r="Z36" s="41">
         <v>0</v>
       </c>
-      <c r="AA36" s="41"/>
-      <c r="AB36" s="41"/>
+      <c r="AA36" s="43"/>
+      <c r="AB36" s="43"/>
       <c r="AC36" s="5"/>
     </row>
     <row r="37" spans="1:29">
@@ -7557,11 +7556,11 @@
       <c r="Y37" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z37" s="44">
+      <c r="Z37" s="41">
         <v>0</v>
       </c>
-      <c r="AA37" s="41"/>
-      <c r="AB37" s="41"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
       <c r="AC37" s="5"/>
     </row>
     <row r="38" spans="1:29">
@@ -7630,11 +7629,11 @@
       <c r="Y38" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z38" s="44">
+      <c r="Z38" s="41">
         <v>0</v>
       </c>
-      <c r="AA38" s="41"/>
-      <c r="AB38" s="41"/>
+      <c r="AA38" s="43"/>
+      <c r="AB38" s="43"/>
       <c r="AC38" s="5"/>
     </row>
     <row r="39" spans="1:29">
@@ -7701,11 +7700,11 @@
       <c r="Y39" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z39" s="44">
+      <c r="Z39" s="41">
         <v>0</v>
       </c>
-      <c r="AA39" s="41"/>
-      <c r="AB39" s="41"/>
+      <c r="AA39" s="43"/>
+      <c r="AB39" s="43"/>
       <c r="AC39" s="5"/>
     </row>
     <row r="40" spans="1:29">
@@ -7772,11 +7771,11 @@
       <c r="Y40" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z40" s="44">
+      <c r="Z40" s="41">
         <v>0</v>
       </c>
-      <c r="AA40" s="41"/>
-      <c r="AB40" s="41"/>
+      <c r="AA40" s="43"/>
+      <c r="AB40" s="43"/>
       <c r="AC40" s="5"/>
     </row>
     <row r="41" spans="1:29">
@@ -7843,11 +7842,11 @@
       <c r="Y41" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z41" s="44">
+      <c r="Z41" s="41">
         <v>0</v>
       </c>
-      <c r="AA41" s="41"/>
-      <c r="AB41" s="41"/>
+      <c r="AA41" s="43"/>
+      <c r="AB41" s="43"/>
       <c r="AC41" s="5"/>
     </row>
     <row r="42" spans="1:29">
@@ -7914,11 +7913,11 @@
       <c r="Y42" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z42" s="44">
+      <c r="Z42" s="41">
         <v>0</v>
       </c>
-      <c r="AA42" s="41"/>
-      <c r="AB42" s="41"/>
+      <c r="AA42" s="43"/>
+      <c r="AB42" s="43"/>
       <c r="AC42" s="5"/>
     </row>
     <row r="43" spans="1:29">
@@ -7985,11 +7984,11 @@
       <c r="Y43" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z43" s="44">
+      <c r="Z43" s="41">
         <v>0</v>
       </c>
-      <c r="AA43" s="41"/>
-      <c r="AB43" s="41"/>
+      <c r="AA43" s="43"/>
+      <c r="AB43" s="43"/>
       <c r="AC43" s="5"/>
     </row>
     <row r="44" spans="1:29">
@@ -8056,11 +8055,11 @@
       <c r="Y44" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z44" s="44">
+      <c r="Z44" s="41">
         <v>0</v>
       </c>
-      <c r="AA44" s="41"/>
-      <c r="AB44" s="41"/>
+      <c r="AA44" s="43"/>
+      <c r="AB44" s="43"/>
       <c r="AC44" s="5"/>
     </row>
     <row r="45" spans="1:29">
@@ -8127,11 +8126,11 @@
       <c r="Y45" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z45" s="44">
+      <c r="Z45" s="41">
         <v>0</v>
       </c>
-      <c r="AA45" s="41"/>
-      <c r="AB45" s="41"/>
+      <c r="AA45" s="43"/>
+      <c r="AB45" s="43"/>
       <c r="AC45" s="5"/>
     </row>
     <row r="46" spans="1:29">
@@ -8198,11 +8197,11 @@
       <c r="Y46" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z46" s="44">
+      <c r="Z46" s="41">
         <v>0</v>
       </c>
-      <c r="AA46" s="41"/>
-      <c r="AB46" s="41"/>
+      <c r="AA46" s="43"/>
+      <c r="AB46" s="43"/>
       <c r="AC46" s="5"/>
     </row>
     <row r="47" spans="1:29">
@@ -8267,11 +8266,11 @@
       <c r="Y47" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z47" s="44">
+      <c r="Z47" s="41">
         <v>0</v>
       </c>
-      <c r="AA47" s="41"/>
-      <c r="AB47" s="41"/>
+      <c r="AA47" s="43"/>
+      <c r="AB47" s="43"/>
       <c r="AC47" s="5"/>
     </row>
     <row r="48" spans="1:29">
@@ -8338,11 +8337,11 @@
       <c r="Y48" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z48" s="44">
+      <c r="Z48" s="41">
         <v>0</v>
       </c>
-      <c r="AA48" s="41"/>
-      <c r="AB48" s="41"/>
+      <c r="AA48" s="43"/>
+      <c r="AB48" s="43"/>
       <c r="AC48" s="5"/>
     </row>
     <row r="49" spans="1:29">
@@ -8407,11 +8406,11 @@
       <c r="Y49" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z49" s="44">
+      <c r="Z49" s="41">
         <v>0</v>
       </c>
-      <c r="AA49" s="41"/>
-      <c r="AB49" s="41"/>
+      <c r="AA49" s="43"/>
+      <c r="AB49" s="43"/>
       <c r="AC49" s="5"/>
     </row>
     <row r="50" spans="1:29">
@@ -8478,11 +8477,11 @@
       <c r="Y50" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z50" s="44">
+      <c r="Z50" s="41">
         <v>0</v>
       </c>
-      <c r="AA50" s="41"/>
-      <c r="AB50" s="41"/>
+      <c r="AA50" s="43"/>
+      <c r="AB50" s="43"/>
       <c r="AC50" s="5"/>
     </row>
     <row r="51" spans="1:29">
@@ -8549,11 +8548,11 @@
       <c r="Y51" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z51" s="44">
+      <c r="Z51" s="41">
         <v>0</v>
       </c>
-      <c r="AA51" s="41"/>
-      <c r="AB51" s="41"/>
+      <c r="AA51" s="43"/>
+      <c r="AB51" s="43"/>
       <c r="AC51" s="5"/>
     </row>
     <row r="52" spans="1:29">
@@ -8618,11 +8617,11 @@
       <c r="Y52" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z52" s="44">
+      <c r="Z52" s="41">
         <v>0</v>
       </c>
-      <c r="AA52" s="41"/>
-      <c r="AB52" s="41"/>
+      <c r="AA52" s="43"/>
+      <c r="AB52" s="43"/>
       <c r="AC52" s="5"/>
     </row>
     <row r="53" spans="1:29">
@@ -8687,11 +8686,11 @@
       <c r="Y53" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z53" s="44">
+      <c r="Z53" s="41">
         <v>0</v>
       </c>
-      <c r="AA53" s="41"/>
-      <c r="AB53" s="41"/>
+      <c r="AA53" s="43"/>
+      <c r="AB53" s="43"/>
       <c r="AC53" s="5"/>
     </row>
     <row r="54" spans="1:29">
@@ -8758,11 +8757,11 @@
       <c r="Y54" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z54" s="44">
+      <c r="Z54" s="41">
         <v>0</v>
       </c>
-      <c r="AA54" s="41"/>
-      <c r="AB54" s="41"/>
+      <c r="AA54" s="43"/>
+      <c r="AB54" s="43"/>
       <c r="AC54" s="5"/>
     </row>
     <row r="55" spans="1:29">
@@ -8827,11 +8826,11 @@
       <c r="Y55" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z55" s="44">
+      <c r="Z55" s="41">
         <v>0</v>
       </c>
-      <c r="AA55" s="41"/>
-      <c r="AB55" s="41"/>
+      <c r="AA55" s="43"/>
+      <c r="AB55" s="43"/>
       <c r="AC55" s="5"/>
     </row>
     <row r="56" spans="1:29" ht="28">
@@ -8896,11 +8895,11 @@
       <c r="Y56" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z56" s="44">
+      <c r="Z56" s="41">
         <v>0</v>
       </c>
-      <c r="AA56" s="41"/>
-      <c r="AB56" s="41"/>
+      <c r="AA56" s="43"/>
+      <c r="AB56" s="43"/>
       <c r="AC56" s="5"/>
     </row>
     <row r="57" spans="1:29">
@@ -8969,11 +8968,11 @@
       <c r="Y57" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z57" s="44">
+      <c r="Z57" s="41">
         <v>0</v>
       </c>
-      <c r="AA57" s="41"/>
-      <c r="AB57" s="41"/>
+      <c r="AA57" s="43"/>
+      <c r="AB57" s="43"/>
       <c r="AC57" s="5"/>
     </row>
     <row r="58" spans="1:29">
@@ -9040,11 +9039,11 @@
       <c r="Y58" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z58" s="44">
+      <c r="Z58" s="41">
         <v>0</v>
       </c>
-      <c r="AA58" s="41"/>
-      <c r="AB58" s="41"/>
+      <c r="AA58" s="43"/>
+      <c r="AB58" s="43"/>
       <c r="AC58" s="5"/>
     </row>
     <row r="59" spans="1:29">
@@ -9111,11 +9110,11 @@
       <c r="Y59" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z59" s="44">
+      <c r="Z59" s="41">
         <v>0</v>
       </c>
-      <c r="AA59" s="41"/>
-      <c r="AB59" s="41"/>
+      <c r="AA59" s="43"/>
+      <c r="AB59" s="43"/>
       <c r="AC59" s="5"/>
     </row>
     <row r="60" spans="1:29">
@@ -9182,11 +9181,11 @@
       <c r="Y60" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z60" s="44">
+      <c r="Z60" s="41">
         <v>0</v>
       </c>
-      <c r="AA60" s="41"/>
-      <c r="AB60" s="41"/>
+      <c r="AA60" s="43"/>
+      <c r="AB60" s="43"/>
       <c r="AC60" s="5"/>
     </row>
     <row r="61" spans="1:29">
@@ -9253,11 +9252,11 @@
       <c r="Y61" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z61" s="44">
+      <c r="Z61" s="41">
         <v>0</v>
       </c>
-      <c r="AA61" s="41"/>
-      <c r="AB61" s="41"/>
+      <c r="AA61" s="43"/>
+      <c r="AB61" s="43"/>
       <c r="AC61" s="5"/>
     </row>
     <row r="62" spans="1:29">
@@ -9322,11 +9321,11 @@
       <c r="Y62" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z62" s="44">
+      <c r="Z62" s="41">
         <v>0</v>
       </c>
-      <c r="AA62" s="41"/>
-      <c r="AB62" s="41"/>
+      <c r="AA62" s="43"/>
+      <c r="AB62" s="43"/>
       <c r="AC62" s="5"/>
     </row>
     <row r="63" spans="1:29">
@@ -9391,11 +9390,11 @@
       <c r="Y63" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z63" s="44">
+      <c r="Z63" s="41">
         <v>0</v>
       </c>
-      <c r="AA63" s="41"/>
-      <c r="AB63" s="41"/>
+      <c r="AA63" s="43"/>
+      <c r="AB63" s="43"/>
       <c r="AC63" s="5"/>
     </row>
     <row r="64" spans="1:29">
@@ -9462,11 +9461,11 @@
       <c r="Y64" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z64" s="44">
+      <c r="Z64" s="41">
         <v>0</v>
       </c>
-      <c r="AA64" s="41"/>
-      <c r="AB64" s="41"/>
+      <c r="AA64" s="43"/>
+      <c r="AB64" s="43"/>
       <c r="AC64" s="5"/>
     </row>
     <row r="65" spans="1:29">
@@ -9531,11 +9530,11 @@
       <c r="Y65" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z65" s="44">
+      <c r="Z65" s="41">
         <v>0</v>
       </c>
-      <c r="AA65" s="41"/>
-      <c r="AB65" s="41"/>
+      <c r="AA65" s="43"/>
+      <c r="AB65" s="43"/>
       <c r="AC65" s="5"/>
     </row>
     <row r="66" spans="1:29">
@@ -9600,11 +9599,11 @@
       <c r="Y66" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z66" s="44">
+      <c r="Z66" s="41">
         <v>0</v>
       </c>
-      <c r="AA66" s="41"/>
-      <c r="AB66" s="41"/>
+      <c r="AA66" s="43"/>
+      <c r="AB66" s="43"/>
       <c r="AC66" s="5"/>
     </row>
     <row r="67" spans="1:29">
@@ -9671,11 +9670,11 @@
       <c r="Y67" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z67" s="44">
+      <c r="Z67" s="41">
         <v>0</v>
       </c>
-      <c r="AA67" s="41"/>
-      <c r="AB67" s="41"/>
+      <c r="AA67" s="43"/>
+      <c r="AB67" s="43"/>
       <c r="AC67" s="5"/>
     </row>
     <row r="68" spans="1:29">
@@ -9742,11 +9741,11 @@
       <c r="Y68" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z68" s="44">
+      <c r="Z68" s="41">
         <v>0</v>
       </c>
-      <c r="AA68" s="41"/>
-      <c r="AB68" s="41"/>
+      <c r="AA68" s="43"/>
+      <c r="AB68" s="43"/>
       <c r="AC68" s="5"/>
     </row>
     <row r="69" spans="1:29">
@@ -9813,11 +9812,11 @@
       <c r="Y69" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z69" s="44">
+      <c r="Z69" s="41">
         <v>0</v>
       </c>
-      <c r="AA69" s="41"/>
-      <c r="AB69" s="41"/>
+      <c r="AA69" s="43"/>
+      <c r="AB69" s="43"/>
       <c r="AC69" s="5"/>
     </row>
     <row r="70" spans="1:29">
@@ -9884,11 +9883,11 @@
       <c r="Y70" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z70" s="44">
+      <c r="Z70" s="41">
         <v>0</v>
       </c>
-      <c r="AA70" s="41"/>
-      <c r="AB70" s="41"/>
+      <c r="AA70" s="43"/>
+      <c r="AB70" s="43"/>
       <c r="AC70" s="5"/>
     </row>
     <row r="71" spans="1:29">
@@ -9955,11 +9954,11 @@
       <c r="Y71" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z71" s="44">
+      <c r="Z71" s="41">
         <v>0</v>
       </c>
-      <c r="AA71" s="41"/>
-      <c r="AB71" s="41"/>
+      <c r="AA71" s="43"/>
+      <c r="AB71" s="43"/>
       <c r="AC71" s="5"/>
     </row>
     <row r="72" spans="1:29">
@@ -10024,11 +10023,11 @@
       <c r="Y72" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z72" s="44">
+      <c r="Z72" s="41">
         <v>0</v>
       </c>
-      <c r="AA72" s="41"/>
-      <c r="AB72" s="41"/>
+      <c r="AA72" s="43"/>
+      <c r="AB72" s="43"/>
       <c r="AC72" s="5"/>
     </row>
     <row r="73" spans="1:29">
@@ -10095,11 +10094,11 @@
       <c r="Y73" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z73" s="44">
+      <c r="Z73" s="41">
         <v>0</v>
       </c>
-      <c r="AA73" s="41"/>
-      <c r="AB73" s="41"/>
+      <c r="AA73" s="43"/>
+      <c r="AB73" s="43"/>
       <c r="AC73" s="5"/>
     </row>
     <row r="74" spans="1:29">
@@ -10166,11 +10165,11 @@
       <c r="Y74" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z74" s="44">
+      <c r="Z74" s="41">
         <v>0</v>
       </c>
-      <c r="AA74" s="41"/>
-      <c r="AB74" s="41"/>
+      <c r="AA74" s="43"/>
+      <c r="AB74" s="43"/>
       <c r="AC74" s="5"/>
     </row>
     <row r="75" spans="1:29">
@@ -10237,11 +10236,11 @@
       <c r="Y75" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z75" s="44">
+      <c r="Z75" s="41">
         <v>0</v>
       </c>
-      <c r="AA75" s="41"/>
-      <c r="AB75" s="41"/>
+      <c r="AA75" s="43"/>
+      <c r="AB75" s="43"/>
       <c r="AC75" s="5"/>
     </row>
     <row r="76" spans="1:29">
@@ -10308,11 +10307,11 @@
       <c r="Y76" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z76" s="44">
+      <c r="Z76" s="41">
         <v>0</v>
       </c>
-      <c r="AA76" s="41"/>
-      <c r="AB76" s="41"/>
+      <c r="AA76" s="43"/>
+      <c r="AB76" s="43"/>
       <c r="AC76" s="5"/>
     </row>
     <row r="77" spans="1:29">
@@ -10377,11 +10376,11 @@
       <c r="Y77" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z77" s="44">
+      <c r="Z77" s="41">
         <v>0</v>
       </c>
-      <c r="AA77" s="41"/>
-      <c r="AB77" s="41"/>
+      <c r="AA77" s="43"/>
+      <c r="AB77" s="43"/>
       <c r="AC77" s="5"/>
     </row>
     <row r="78" spans="1:29">
@@ -10446,11 +10445,11 @@
       <c r="Y78" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z78" s="44">
+      <c r="Z78" s="41">
         <v>0</v>
       </c>
-      <c r="AA78" s="41"/>
-      <c r="AB78" s="41"/>
+      <c r="AA78" s="43"/>
+      <c r="AB78" s="43"/>
       <c r="AC78" s="5"/>
     </row>
     <row r="79" spans="1:29">
@@ -10515,11 +10514,11 @@
       <c r="Y79" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z79" s="44">
+      <c r="Z79" s="41">
         <v>0</v>
       </c>
-      <c r="AA79" s="41"/>
-      <c r="AB79" s="41"/>
+      <c r="AA79" s="43"/>
+      <c r="AB79" s="43"/>
       <c r="AC79" s="5"/>
     </row>
     <row r="80" spans="1:29">
@@ -10586,11 +10585,11 @@
       <c r="Y80" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z80" s="44">
+      <c r="Z80" s="41">
         <v>0</v>
       </c>
-      <c r="AA80" s="41"/>
-      <c r="AB80" s="41"/>
+      <c r="AA80" s="43"/>
+      <c r="AB80" s="43"/>
       <c r="AC80" s="5"/>
     </row>
     <row r="81" spans="1:29">
@@ -10655,11 +10654,11 @@
       <c r="Y81" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z81" s="44">
+      <c r="Z81" s="41">
         <v>0</v>
       </c>
-      <c r="AA81" s="41"/>
-      <c r="AB81" s="41"/>
+      <c r="AA81" s="43"/>
+      <c r="AB81" s="43"/>
       <c r="AC81" s="5"/>
     </row>
     <row r="82" spans="1:29">
@@ -10724,11 +10723,11 @@
       <c r="Y82" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z82" s="44">
+      <c r="Z82" s="41">
         <v>0</v>
       </c>
-      <c r="AA82" s="41"/>
-      <c r="AB82" s="41"/>
+      <c r="AA82" s="43"/>
+      <c r="AB82" s="43"/>
       <c r="AC82" s="5"/>
     </row>
     <row r="83" spans="1:29">
@@ -10793,11 +10792,11 @@
       <c r="Y83" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z83" s="44">
+      <c r="Z83" s="41">
         <v>0</v>
       </c>
-      <c r="AA83" s="41"/>
-      <c r="AB83" s="41"/>
+      <c r="AA83" s="43"/>
+      <c r="AB83" s="43"/>
       <c r="AC83" s="5"/>
     </row>
     <row r="84" spans="1:29">
@@ -10864,11 +10863,11 @@
       <c r="Y84" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z84" s="44">
+      <c r="Z84" s="41">
         <v>0</v>
       </c>
-      <c r="AA84" s="41"/>
-      <c r="AB84" s="41"/>
+      <c r="AA84" s="43"/>
+      <c r="AB84" s="43"/>
       <c r="AC84" s="5"/>
     </row>
     <row r="85" spans="1:29">
@@ -10935,11 +10934,11 @@
       <c r="Y85" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z85" s="44">
+      <c r="Z85" s="41">
         <v>0</v>
       </c>
-      <c r="AA85" s="41"/>
-      <c r="AB85" s="41"/>
+      <c r="AA85" s="43"/>
+      <c r="AB85" s="43"/>
       <c r="AC85" s="5"/>
     </row>
     <row r="86" spans="1:29">
@@ -11004,11 +11003,11 @@
       <c r="Y86" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z86" s="44">
+      <c r="Z86" s="41">
         <v>0</v>
       </c>
-      <c r="AA86" s="41"/>
-      <c r="AB86" s="41"/>
+      <c r="AA86" s="43"/>
+      <c r="AB86" s="43"/>
       <c r="AC86" s="5"/>
     </row>
     <row r="87" spans="1:29">
@@ -11075,11 +11074,11 @@
       <c r="Y87" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z87" s="44">
+      <c r="Z87" s="41">
         <v>0</v>
       </c>
-      <c r="AA87" s="41"/>
-      <c r="AB87" s="41"/>
+      <c r="AA87" s="43"/>
+      <c r="AB87" s="43"/>
       <c r="AC87" s="5"/>
     </row>
     <row r="88" spans="1:29">
@@ -11146,11 +11145,11 @@
       <c r="Y88" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z88" s="44">
+      <c r="Z88" s="41">
         <v>0</v>
       </c>
-      <c r="AA88" s="41"/>
-      <c r="AB88" s="41"/>
+      <c r="AA88" s="43"/>
+      <c r="AB88" s="43"/>
       <c r="AC88" s="5"/>
     </row>
     <row r="89" spans="1:29">
@@ -11217,11 +11216,11 @@
       <c r="Y89" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z89" s="44">
+      <c r="Z89" s="41">
         <v>0</v>
       </c>
-      <c r="AA89" s="41"/>
-      <c r="AB89" s="41"/>
+      <c r="AA89" s="43"/>
+      <c r="AB89" s="43"/>
       <c r="AC89" s="5"/>
     </row>
     <row r="90" spans="1:29">
@@ -11290,11 +11289,11 @@
       <c r="Y90" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z90" s="44">
+      <c r="Z90" s="41">
         <v>0</v>
       </c>
-      <c r="AA90" s="41"/>
-      <c r="AB90" s="41"/>
+      <c r="AA90" s="43"/>
+      <c r="AB90" s="43"/>
       <c r="AC90" s="5"/>
     </row>
     <row r="91" spans="1:29">
@@ -11363,11 +11362,11 @@
       <c r="Y91" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z91" s="44">
+      <c r="Z91" s="41">
         <v>0</v>
       </c>
-      <c r="AA91" s="41"/>
-      <c r="AB91" s="41"/>
+      <c r="AA91" s="43"/>
+      <c r="AB91" s="43"/>
       <c r="AC91" s="5"/>
     </row>
     <row r="92" spans="1:29">
@@ -11434,11 +11433,11 @@
       <c r="Y92" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z92" s="44">
+      <c r="Z92" s="41">
         <v>0</v>
       </c>
-      <c r="AA92" s="41"/>
-      <c r="AB92" s="41"/>
+      <c r="AA92" s="43"/>
+      <c r="AB92" s="43"/>
       <c r="AC92" s="5"/>
     </row>
     <row r="93" spans="1:29">
@@ -11505,11 +11504,11 @@
       <c r="Y93" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z93" s="44">
+      <c r="Z93" s="41">
         <v>0</v>
       </c>
-      <c r="AA93" s="41"/>
-      <c r="AB93" s="41"/>
+      <c r="AA93" s="43"/>
+      <c r="AB93" s="43"/>
       <c r="AC93" s="5"/>
     </row>
     <row r="94" spans="1:29">
@@ -11576,11 +11575,11 @@
       <c r="Y94" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z94" s="44">
+      <c r="Z94" s="41">
         <v>0</v>
       </c>
-      <c r="AA94" s="41"/>
-      <c r="AB94" s="41"/>
+      <c r="AA94" s="43"/>
+      <c r="AB94" s="43"/>
       <c r="AC94" s="5"/>
     </row>
     <row r="95" spans="1:29">
@@ -11649,11 +11648,11 @@
       <c r="Y95" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z95" s="44">
+      <c r="Z95" s="41">
         <v>0</v>
       </c>
-      <c r="AA95" s="41"/>
-      <c r="AB95" s="41"/>
+      <c r="AA95" s="43"/>
+      <c r="AB95" s="43"/>
       <c r="AC95" s="5"/>
     </row>
     <row r="96" spans="1:29">
@@ -11722,11 +11721,11 @@
       <c r="Y96" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z96" s="44">
+      <c r="Z96" s="41">
         <v>0</v>
       </c>
-      <c r="AA96" s="41"/>
-      <c r="AB96" s="41"/>
+      <c r="AA96" s="43"/>
+      <c r="AB96" s="43"/>
       <c r="AC96" s="5"/>
     </row>
     <row r="97" spans="1:29">
@@ -11795,11 +11794,11 @@
       <c r="Y97" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z97" s="44">
+      <c r="Z97" s="41">
         <v>0</v>
       </c>
-      <c r="AA97" s="41"/>
-      <c r="AB97" s="41"/>
+      <c r="AA97" s="43"/>
+      <c r="AB97" s="43"/>
       <c r="AC97" s="5"/>
     </row>
     <row r="98" spans="1:29">
@@ -11868,11 +11867,11 @@
       <c r="Y98" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z98" s="44">
+      <c r="Z98" s="41">
         <v>0</v>
       </c>
-      <c r="AA98" s="41"/>
-      <c r="AB98" s="41"/>
+      <c r="AA98" s="43"/>
+      <c r="AB98" s="43"/>
       <c r="AC98" s="5"/>
     </row>
     <row r="99" spans="1:29">
@@ -11937,11 +11936,11 @@
       <c r="Y99" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z99" s="44">
+      <c r="Z99" s="41">
         <v>0</v>
       </c>
-      <c r="AA99" s="41"/>
-      <c r="AB99" s="41"/>
+      <c r="AA99" s="43"/>
+      <c r="AB99" s="43"/>
       <c r="AC99" s="5"/>
     </row>
     <row r="100" spans="1:29">
@@ -12008,11 +12007,11 @@
       <c r="Y100" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z100" s="44">
+      <c r="Z100" s="41">
         <v>0</v>
       </c>
-      <c r="AA100" s="41"/>
-      <c r="AB100" s="41"/>
+      <c r="AA100" s="43"/>
+      <c r="AB100" s="43"/>
       <c r="AC100" s="5"/>
     </row>
     <row r="101" spans="1:29">
@@ -12079,11 +12078,11 @@
       <c r="Y101" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z101" s="44">
+      <c r="Z101" s="41">
         <v>0</v>
       </c>
-      <c r="AA101" s="41"/>
-      <c r="AB101" s="41"/>
+      <c r="AA101" s="43"/>
+      <c r="AB101" s="43"/>
       <c r="AC101" s="5"/>
     </row>
     <row r="102" spans="1:29">
@@ -12150,11 +12149,11 @@
       <c r="Y102" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z102" s="44">
+      <c r="Z102" s="41">
         <v>0</v>
       </c>
-      <c r="AA102" s="41"/>
-      <c r="AB102" s="41"/>
+      <c r="AA102" s="43"/>
+      <c r="AB102" s="43"/>
       <c r="AC102" s="5"/>
     </row>
     <row r="103" spans="1:29">
@@ -12221,11 +12220,11 @@
       <c r="Y103" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z103" s="44">
+      <c r="Z103" s="41">
         <v>0</v>
       </c>
-      <c r="AA103" s="41"/>
-      <c r="AB103" s="41"/>
+      <c r="AA103" s="43"/>
+      <c r="AB103" s="43"/>
       <c r="AC103" s="5"/>
     </row>
     <row r="104" spans="1:29">
@@ -12290,11 +12289,11 @@
       <c r="Y104" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z104" s="44">
+      <c r="Z104" s="41">
         <v>0</v>
       </c>
-      <c r="AA104" s="41"/>
-      <c r="AB104" s="41"/>
+      <c r="AA104" s="43"/>
+      <c r="AB104" s="43"/>
       <c r="AC104" s="5"/>
     </row>
     <row r="105" spans="1:29">
@@ -12359,11 +12358,11 @@
       <c r="Y105" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z105" s="44">
+      <c r="Z105" s="41">
         <v>0</v>
       </c>
-      <c r="AA105" s="41"/>
-      <c r="AB105" s="41"/>
+      <c r="AA105" s="43"/>
+      <c r="AB105" s="43"/>
       <c r="AC105" s="5"/>
     </row>
     <row r="106" spans="1:29">
@@ -12428,11 +12427,11 @@
       <c r="Y106" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z106" s="44">
+      <c r="Z106" s="41">
         <v>0</v>
       </c>
-      <c r="AA106" s="41"/>
-      <c r="AB106" s="41"/>
+      <c r="AA106" s="43"/>
+      <c r="AB106" s="43"/>
       <c r="AC106" s="5"/>
     </row>
     <row r="107" spans="1:29">
@@ -12497,11 +12496,11 @@
       <c r="Y107" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z107" s="44">
+      <c r="Z107" s="41">
         <v>0</v>
       </c>
-      <c r="AA107" s="41"/>
-      <c r="AB107" s="41"/>
+      <c r="AA107" s="43"/>
+      <c r="AB107" s="43"/>
       <c r="AC107" s="5"/>
     </row>
     <row r="108" spans="1:29">
@@ -12566,11 +12565,11 @@
       <c r="Y108" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z108" s="44">
+      <c r="Z108" s="41">
         <v>0</v>
       </c>
-      <c r="AA108" s="41"/>
-      <c r="AB108" s="41"/>
+      <c r="AA108" s="43"/>
+      <c r="AB108" s="43"/>
       <c r="AC108" s="5"/>
     </row>
     <row r="109" spans="1:29">
@@ -12635,11 +12634,11 @@
       <c r="Y109" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z109" s="44">
+      <c r="Z109" s="41">
         <v>0</v>
       </c>
-      <c r="AA109" s="41"/>
-      <c r="AB109" s="41"/>
+      <c r="AA109" s="43"/>
+      <c r="AB109" s="43"/>
       <c r="AC109" s="5"/>
     </row>
     <row r="110" spans="1:29">
@@ -12706,11 +12705,11 @@
       <c r="Y110" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z110" s="44">
+      <c r="Z110" s="41">
         <v>0</v>
       </c>
-      <c r="AA110" s="41"/>
-      <c r="AB110" s="41"/>
+      <c r="AA110" s="43"/>
+      <c r="AB110" s="43"/>
       <c r="AC110" s="5"/>
     </row>
     <row r="111" spans="1:29">
@@ -12775,11 +12774,11 @@
       <c r="Y111" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z111" s="44">
+      <c r="Z111" s="41">
         <v>0</v>
       </c>
-      <c r="AA111" s="41"/>
-      <c r="AB111" s="41"/>
+      <c r="AA111" s="43"/>
+      <c r="AB111" s="43"/>
       <c r="AC111" s="5"/>
     </row>
     <row r="112" spans="1:29">
@@ -12844,11 +12843,11 @@
       <c r="Y112" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z112" s="44">
+      <c r="Z112" s="41">
         <v>0</v>
       </c>
-      <c r="AA112" s="41"/>
-      <c r="AB112" s="41"/>
+      <c r="AA112" s="43"/>
+      <c r="AB112" s="43"/>
       <c r="AC112" s="5"/>
     </row>
     <row r="113" spans="1:29">
@@ -12915,11 +12914,11 @@
       <c r="Y113" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z113" s="44">
+      <c r="Z113" s="41">
         <v>0</v>
       </c>
-      <c r="AA113" s="41"/>
-      <c r="AB113" s="41"/>
+      <c r="AA113" s="43"/>
+      <c r="AB113" s="43"/>
       <c r="AC113" s="5"/>
     </row>
     <row r="114" spans="1:29">
@@ -12984,11 +12983,11 @@
       <c r="Y114" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z114" s="44">
+      <c r="Z114" s="41">
         <v>0</v>
       </c>
-      <c r="AA114" s="41"/>
-      <c r="AB114" s="41"/>
+      <c r="AA114" s="43"/>
+      <c r="AB114" s="43"/>
       <c r="AC114" s="5"/>
     </row>
     <row r="115" spans="1:29">
@@ -13053,11 +13052,11 @@
       <c r="Y115" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z115" s="44">
+      <c r="Z115" s="41">
         <v>0</v>
       </c>
-      <c r="AA115" s="41"/>
-      <c r="AB115" s="41"/>
+      <c r="AA115" s="43"/>
+      <c r="AB115" s="43"/>
       <c r="AC115" s="5"/>
     </row>
     <row r="116" spans="1:29">
@@ -13122,11 +13121,11 @@
       <c r="Y116" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z116" s="44">
+      <c r="Z116" s="41">
         <v>0</v>
       </c>
-      <c r="AA116" s="41"/>
-      <c r="AB116" s="41"/>
+      <c r="AA116" s="43"/>
+      <c r="AB116" s="43"/>
       <c r="AC116" s="5"/>
     </row>
     <row r="117" spans="1:29">
@@ -13193,11 +13192,11 @@
       <c r="Y117" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z117" s="44">
+      <c r="Z117" s="41">
         <v>0</v>
       </c>
-      <c r="AA117" s="41"/>
-      <c r="AB117" s="41"/>
+      <c r="AA117" s="43"/>
+      <c r="AB117" s="43"/>
       <c r="AC117" s="5"/>
     </row>
     <row r="118" spans="1:29">
@@ -13262,11 +13261,11 @@
       <c r="Y118" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z118" s="44">
+      <c r="Z118" s="41">
         <v>0</v>
       </c>
-      <c r="AA118" s="41"/>
-      <c r="AB118" s="41"/>
+      <c r="AA118" s="43"/>
+      <c r="AB118" s="43"/>
       <c r="AC118" s="5"/>
     </row>
     <row r="119" spans="1:29">
@@ -13331,11 +13330,11 @@
       <c r="Y119" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z119" s="44">
+      <c r="Z119" s="41">
         <v>0</v>
       </c>
-      <c r="AA119" s="41"/>
-      <c r="AB119" s="41"/>
+      <c r="AA119" s="43"/>
+      <c r="AB119" s="43"/>
       <c r="AC119" s="5"/>
     </row>
     <row r="120" spans="1:29">
@@ -13400,11 +13399,11 @@
       <c r="Y120" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z120" s="44">
+      <c r="Z120" s="41">
         <v>0</v>
       </c>
-      <c r="AA120" s="41"/>
-      <c r="AB120" s="41"/>
+      <c r="AA120" s="43"/>
+      <c r="AB120" s="43"/>
       <c r="AC120" s="5"/>
     </row>
     <row r="121" spans="1:29">
@@ -13471,11 +13470,11 @@
       <c r="Y121" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z121" s="44">
+      <c r="Z121" s="41">
         <v>0</v>
       </c>
-      <c r="AA121" s="41"/>
-      <c r="AB121" s="41"/>
+      <c r="AA121" s="43"/>
+      <c r="AB121" s="43"/>
       <c r="AC121" s="5"/>
     </row>
     <row r="122" spans="1:29">
@@ -13542,11 +13541,11 @@
       <c r="Y122" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z122" s="44">
+      <c r="Z122" s="41">
         <v>0</v>
       </c>
-      <c r="AA122" s="41"/>
-      <c r="AB122" s="41"/>
+      <c r="AA122" s="43"/>
+      <c r="AB122" s="43"/>
       <c r="AC122" s="5"/>
     </row>
     <row r="123" spans="1:29">
@@ -13613,11 +13612,11 @@
       <c r="Y123" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z123" s="44">
+      <c r="Z123" s="41">
         <v>0</v>
       </c>
-      <c r="AA123" s="41"/>
-      <c r="AB123" s="41"/>
+      <c r="AA123" s="43"/>
+      <c r="AB123" s="43"/>
       <c r="AC123" s="5"/>
     </row>
     <row r="124" spans="1:29">
@@ -13684,11 +13683,11 @@
       <c r="Y124" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z124" s="44">
+      <c r="Z124" s="41">
         <v>0</v>
       </c>
-      <c r="AA124" s="41"/>
-      <c r="AB124" s="41"/>
+      <c r="AA124" s="43"/>
+      <c r="AB124" s="43"/>
       <c r="AC124" s="5"/>
     </row>
     <row r="125" spans="1:29">
@@ -13755,11 +13754,11 @@
       <c r="Y125" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z125" s="44">
+      <c r="Z125" s="41">
         <v>0</v>
       </c>
-      <c r="AA125" s="41"/>
-      <c r="AB125" s="41"/>
+      <c r="AA125" s="43"/>
+      <c r="AB125" s="43"/>
       <c r="AC125" s="5"/>
     </row>
     <row r="126" spans="1:29">
@@ -13826,11 +13825,11 @@
       <c r="Y126" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z126" s="44">
+      <c r="Z126" s="41">
         <v>0</v>
       </c>
-      <c r="AA126" s="41"/>
-      <c r="AB126" s="41"/>
+      <c r="AA126" s="43"/>
+      <c r="AB126" s="43"/>
       <c r="AC126" s="5"/>
     </row>
     <row r="127" spans="1:29">
@@ -13899,11 +13898,11 @@
       <c r="Y127" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z127" s="44">
+      <c r="Z127" s="41">
         <v>0</v>
       </c>
-      <c r="AA127" s="41"/>
-      <c r="AB127" s="41"/>
+      <c r="AA127" s="43"/>
+      <c r="AB127" s="43"/>
       <c r="AC127" s="5"/>
     </row>
     <row r="128" spans="1:29">
@@ -13970,11 +13969,11 @@
       <c r="Y128" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z128" s="44">
+      <c r="Z128" s="41">
         <v>0</v>
       </c>
-      <c r="AA128" s="41"/>
-      <c r="AB128" s="41"/>
+      <c r="AA128" s="43"/>
+      <c r="AB128" s="43"/>
       <c r="AC128" s="5"/>
     </row>
     <row r="129" spans="1:29">
@@ -14043,11 +14042,11 @@
       <c r="Y129" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z129" s="44">
+      <c r="Z129" s="41">
         <v>0</v>
       </c>
-      <c r="AA129" s="41"/>
-      <c r="AB129" s="41"/>
+      <c r="AA129" s="43"/>
+      <c r="AB129" s="43"/>
       <c r="AC129" s="5"/>
     </row>
     <row r="130" spans="1:29">
@@ -14114,11 +14113,11 @@
       <c r="Y130" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z130" s="44">
+      <c r="Z130" s="41">
         <v>0</v>
       </c>
-      <c r="AA130" s="41"/>
-      <c r="AB130" s="41"/>
+      <c r="AA130" s="43"/>
+      <c r="AB130" s="43"/>
       <c r="AC130" s="5"/>
     </row>
     <row r="131" spans="1:29">
@@ -14185,11 +14184,11 @@
       <c r="Y131" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z131" s="44">
+      <c r="Z131" s="41">
         <v>0</v>
       </c>
-      <c r="AA131" s="41"/>
-      <c r="AB131" s="41"/>
+      <c r="AA131" s="43"/>
+      <c r="AB131" s="43"/>
       <c r="AC131" s="5"/>
     </row>
     <row r="132" spans="1:29">
@@ -14256,11 +14255,11 @@
       <c r="Y132" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z132" s="44">
+      <c r="Z132" s="41">
         <v>0</v>
       </c>
-      <c r="AA132" s="41"/>
-      <c r="AB132" s="41"/>
+      <c r="AA132" s="43"/>
+      <c r="AB132" s="43"/>
       <c r="AC132" s="5"/>
     </row>
     <row r="133" spans="1:29">
@@ -14329,11 +14328,11 @@
       <c r="Y133" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z133" s="44">
+      <c r="Z133" s="41">
         <v>0</v>
       </c>
-      <c r="AA133" s="41"/>
-      <c r="AB133" s="41"/>
+      <c r="AA133" s="43"/>
+      <c r="AB133" s="43"/>
       <c r="AC133" s="5"/>
     </row>
     <row r="134" spans="1:29">
@@ -14402,11 +14401,11 @@
       <c r="Y134" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z134" s="44">
+      <c r="Z134" s="41">
         <v>0</v>
       </c>
-      <c r="AA134" s="41"/>
-      <c r="AB134" s="41"/>
+      <c r="AA134" s="43"/>
+      <c r="AB134" s="43"/>
       <c r="AC134" s="5"/>
     </row>
     <row r="135" spans="1:29">
@@ -14475,11 +14474,11 @@
       <c r="Y135" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z135" s="44">
+      <c r="Z135" s="41">
         <v>0</v>
       </c>
-      <c r="AA135" s="41"/>
-      <c r="AB135" s="41"/>
+      <c r="AA135" s="43"/>
+      <c r="AB135" s="43"/>
       <c r="AC135" s="5"/>
     </row>
     <row r="136" spans="1:29">
@@ -14548,11 +14547,11 @@
       <c r="Y136" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z136" s="44">
+      <c r="Z136" s="41">
         <v>0</v>
       </c>
-      <c r="AA136" s="41"/>
-      <c r="AB136" s="41"/>
+      <c r="AA136" s="43"/>
+      <c r="AB136" s="43"/>
       <c r="AC136" s="5"/>
     </row>
     <row r="137" spans="1:29">
@@ -14621,11 +14620,11 @@
       <c r="Y137" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z137" s="44">
+      <c r="Z137" s="41">
         <v>0</v>
       </c>
-      <c r="AA137" s="41"/>
-      <c r="AB137" s="41"/>
+      <c r="AA137" s="43"/>
+      <c r="AB137" s="43"/>
       <c r="AC137" s="5"/>
     </row>
     <row r="138" spans="1:29">
@@ -14694,11 +14693,11 @@
       <c r="Y138" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z138" s="44">
+      <c r="Z138" s="41">
         <v>0</v>
       </c>
-      <c r="AA138" s="41"/>
-      <c r="AB138" s="41"/>
+      <c r="AA138" s="43"/>
+      <c r="AB138" s="43"/>
       <c r="AC138" s="5"/>
     </row>
     <row r="139" spans="1:29">
@@ -14767,11 +14766,11 @@
       <c r="Y139" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z139" s="44">
+      <c r="Z139" s="41">
         <v>0</v>
       </c>
-      <c r="AA139" s="41"/>
-      <c r="AB139" s="41"/>
+      <c r="AA139" s="43"/>
+      <c r="AB139" s="43"/>
       <c r="AC139" s="5"/>
     </row>
     <row r="140" spans="1:29">
@@ -14840,11 +14839,11 @@
       <c r="Y140" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z140" s="44">
+      <c r="Z140" s="41">
         <v>0</v>
       </c>
-      <c r="AA140" s="41"/>
-      <c r="AB140" s="41"/>
+      <c r="AA140" s="43"/>
+      <c r="AB140" s="43"/>
       <c r="AC140" s="5"/>
     </row>
     <row r="141" spans="1:29">
@@ -14913,11 +14912,11 @@
       <c r="Y141" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z141" s="44">
+      <c r="Z141" s="41">
         <v>0</v>
       </c>
-      <c r="AA141" s="41"/>
-      <c r="AB141" s="41"/>
+      <c r="AA141" s="43"/>
+      <c r="AB141" s="43"/>
       <c r="AC141" s="5"/>
     </row>
     <row r="142" spans="1:29">
@@ -14984,11 +14983,11 @@
       <c r="Y142" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z142" s="44">
+      <c r="Z142" s="41">
         <v>0</v>
       </c>
-      <c r="AA142" s="41"/>
-      <c r="AB142" s="41"/>
+      <c r="AA142" s="43"/>
+      <c r="AB142" s="43"/>
       <c r="AC142" s="5"/>
     </row>
     <row r="143" spans="1:29">
@@ -15055,11 +15054,11 @@
       <c r="Y143" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z143" s="44">
+      <c r="Z143" s="41">
         <v>0</v>
       </c>
-      <c r="AA143" s="41"/>
-      <c r="AB143" s="41"/>
+      <c r="AA143" s="43"/>
+      <c r="AB143" s="43"/>
       <c r="AC143" s="5"/>
     </row>
     <row r="144" spans="1:29">
@@ -15126,11 +15125,11 @@
       <c r="Y144" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z144" s="44">
+      <c r="Z144" s="41">
         <v>0</v>
       </c>
-      <c r="AA144" s="41"/>
-      <c r="AB144" s="41"/>
+      <c r="AA144" s="43"/>
+      <c r="AB144" s="43"/>
       <c r="AC144" s="5"/>
     </row>
     <row r="145" spans="1:29">
@@ -15197,11 +15196,11 @@
       <c r="Y145" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z145" s="44">
+      <c r="Z145" s="41">
         <v>0</v>
       </c>
-      <c r="AA145" s="41"/>
-      <c r="AB145" s="41"/>
+      <c r="AA145" s="43"/>
+      <c r="AB145" s="43"/>
       <c r="AC145" s="5"/>
     </row>
     <row r="146" spans="1:29">
@@ -15266,11 +15265,11 @@
       <c r="Y146" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z146" s="44">
+      <c r="Z146" s="41">
         <v>0</v>
       </c>
-      <c r="AA146" s="41"/>
-      <c r="AB146" s="41"/>
+      <c r="AA146" s="43"/>
+      <c r="AB146" s="43"/>
       <c r="AC146" s="5"/>
     </row>
     <row r="147" spans="1:29">
@@ -15337,11 +15336,11 @@
       <c r="Y147" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z147" s="44">
+      <c r="Z147" s="41">
         <v>0</v>
       </c>
-      <c r="AA147" s="41"/>
-      <c r="AB147" s="41"/>
+      <c r="AA147" s="43"/>
+      <c r="AB147" s="43"/>
       <c r="AC147" s="5"/>
     </row>
     <row r="148" spans="1:29">
@@ -15408,11 +15407,11 @@
       <c r="Y148" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z148" s="44">
+      <c r="Z148" s="41">
         <v>0</v>
       </c>
-      <c r="AA148" s="41"/>
-      <c r="AB148" s="41"/>
+      <c r="AA148" s="43"/>
+      <c r="AB148" s="43"/>
       <c r="AC148" s="5"/>
     </row>
     <row r="149" spans="1:29">
@@ -15481,11 +15480,11 @@
       <c r="Y149" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z149" s="44">
+      <c r="Z149" s="41">
         <v>0</v>
       </c>
-      <c r="AA149" s="41"/>
-      <c r="AB149" s="41"/>
+      <c r="AA149" s="43"/>
+      <c r="AB149" s="43"/>
       <c r="AC149" s="5"/>
     </row>
     <row r="150" spans="1:29" ht="28">
@@ -15550,11 +15549,11 @@
       <c r="Y150" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z150" s="44">
+      <c r="Z150" s="41">
         <v>0</v>
       </c>
-      <c r="AA150" s="41"/>
-      <c r="AB150" s="41"/>
+      <c r="AA150" s="43"/>
+      <c r="AB150" s="43"/>
       <c r="AC150" s="5"/>
     </row>
     <row r="151" spans="1:29">
@@ -15621,11 +15620,11 @@
       <c r="Y151" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z151" s="44">
+      <c r="Z151" s="41">
         <v>0</v>
       </c>
-      <c r="AA151" s="41"/>
-      <c r="AB151" s="41"/>
+      <c r="AA151" s="43"/>
+      <c r="AB151" s="43"/>
       <c r="AC151" s="5"/>
     </row>
     <row r="152" spans="1:29">
@@ -15692,11 +15691,11 @@
       <c r="Y152" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z152" s="44">
+      <c r="Z152" s="41">
         <v>0</v>
       </c>
-      <c r="AA152" s="41"/>
-      <c r="AB152" s="41"/>
+      <c r="AA152" s="43"/>
+      <c r="AB152" s="43"/>
       <c r="AC152" s="5"/>
     </row>
     <row r="153" spans="1:29">
@@ -15761,11 +15760,11 @@
       <c r="Y153" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z153" s="44">
+      <c r="Z153" s="41">
         <v>0</v>
       </c>
-      <c r="AA153" s="41"/>
-      <c r="AB153" s="41"/>
+      <c r="AA153" s="43"/>
+      <c r="AB153" s="43"/>
       <c r="AC153" s="5"/>
     </row>
     <row r="154" spans="1:29">
@@ -15832,11 +15831,11 @@
       <c r="Y154" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z154" s="44">
+      <c r="Z154" s="41">
         <v>0</v>
       </c>
-      <c r="AA154" s="41"/>
-      <c r="AB154" s="41"/>
+      <c r="AA154" s="43"/>
+      <c r="AB154" s="43"/>
       <c r="AC154" s="5"/>
     </row>
     <row r="155" spans="1:29">
@@ -15903,11 +15902,11 @@
       <c r="Y155" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z155" s="44">
+      <c r="Z155" s="41">
         <v>0</v>
       </c>
-      <c r="AA155" s="41"/>
-      <c r="AB155" s="41"/>
+      <c r="AA155" s="43"/>
+      <c r="AB155" s="43"/>
       <c r="AC155" s="5"/>
     </row>
     <row r="156" spans="1:29">
@@ -15974,11 +15973,11 @@
       <c r="Y156" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z156" s="44">
+      <c r="Z156" s="41">
         <v>0</v>
       </c>
-      <c r="AA156" s="41"/>
-      <c r="AB156" s="41"/>
+      <c r="AA156" s="43"/>
+      <c r="AB156" s="43"/>
       <c r="AC156" s="5"/>
     </row>
     <row r="157" spans="1:29">
@@ -16047,11 +16046,11 @@
       <c r="Y157" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z157" s="44">
+      <c r="Z157" s="41">
         <v>0</v>
       </c>
-      <c r="AA157" s="41"/>
-      <c r="AB157" s="41"/>
+      <c r="AA157" s="43"/>
+      <c r="AB157" s="43"/>
       <c r="AC157" s="5"/>
     </row>
     <row r="158" spans="1:29" ht="28">
@@ -16116,11 +16115,11 @@
       <c r="Y158" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z158" s="44">
+      <c r="Z158" s="41">
         <v>0</v>
       </c>
-      <c r="AA158" s="41"/>
-      <c r="AB158" s="41"/>
+      <c r="AA158" s="43"/>
+      <c r="AB158" s="43"/>
       <c r="AC158" s="5"/>
     </row>
     <row r="159" spans="1:29" ht="28">
@@ -16185,11 +16184,11 @@
       <c r="Y159" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z159" s="44">
+      <c r="Z159" s="41">
         <v>0</v>
       </c>
-      <c r="AA159" s="41"/>
-      <c r="AB159" s="41"/>
+      <c r="AA159" s="43"/>
+      <c r="AB159" s="43"/>
       <c r="AC159" s="5"/>
     </row>
     <row r="160" spans="1:29">
@@ -16256,11 +16255,11 @@
       <c r="Y160" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z160" s="44">
+      <c r="Z160" s="41">
         <v>0</v>
       </c>
-      <c r="AA160" s="41"/>
-      <c r="AB160" s="41"/>
+      <c r="AA160" s="43"/>
+      <c r="AB160" s="43"/>
       <c r="AC160" s="5"/>
     </row>
     <row r="161" spans="1:29">
@@ -16329,11 +16328,11 @@
       <c r="Y161" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z161" s="44">
+      <c r="Z161" s="41">
         <v>0</v>
       </c>
-      <c r="AA161" s="41"/>
-      <c r="AB161" s="41"/>
+      <c r="AA161" s="43"/>
+      <c r="AB161" s="43"/>
       <c r="AC161" s="5"/>
     </row>
     <row r="162" spans="1:29">
@@ -16400,11 +16399,11 @@
       <c r="Y162" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z162" s="44">
+      <c r="Z162" s="41">
         <v>0</v>
       </c>
-      <c r="AA162" s="41"/>
-      <c r="AB162" s="41"/>
+      <c r="AA162" s="43"/>
+      <c r="AB162" s="43"/>
       <c r="AC162" s="5"/>
     </row>
     <row r="163" spans="1:29">
@@ -16471,11 +16470,11 @@
       <c r="Y163" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z163" s="44">
+      <c r="Z163" s="41">
         <v>0</v>
       </c>
-      <c r="AA163" s="41"/>
-      <c r="AB163" s="41"/>
+      <c r="AA163" s="43"/>
+      <c r="AB163" s="43"/>
       <c r="AC163" s="5"/>
     </row>
     <row r="164" spans="1:29">
@@ -16542,11 +16541,11 @@
       <c r="Y164" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z164" s="44">
+      <c r="Z164" s="41">
         <v>0</v>
       </c>
-      <c r="AA164" s="41"/>
-      <c r="AB164" s="41"/>
+      <c r="AA164" s="43"/>
+      <c r="AB164" s="43"/>
       <c r="AC164" s="5"/>
     </row>
     <row r="165" spans="1:29">
@@ -16613,11 +16612,11 @@
       <c r="Y165" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z165" s="44">
+      <c r="Z165" s="41">
         <v>0</v>
       </c>
-      <c r="AA165" s="41"/>
-      <c r="AB165" s="41"/>
+      <c r="AA165" s="43"/>
+      <c r="AB165" s="43"/>
       <c r="AC165" s="5"/>
     </row>
     <row r="166" spans="1:29">
@@ -16686,11 +16685,11 @@
       <c r="Y166" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="Z166" s="44">
+      <c r="Z166" s="41">
         <v>0</v>
       </c>
-      <c r="AA166" s="41"/>
-      <c r="AB166" s="41"/>
+      <c r="AA166" s="43"/>
+      <c r="AB166" s="43"/>
       <c r="AC166" s="5"/>
     </row>
     <row r="167" spans="1:29">
@@ -16759,11 +16758,11 @@
       <c r="Y167" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="Z167" s="45">
+      <c r="Z167" s="42">
         <v>0</v>
       </c>
-      <c r="AA167" s="42"/>
-      <c r="AB167" s="42"/>
+      <c r="AA167" s="45"/>
+      <c r="AB167" s="45"/>
       <c r="AC167" s="6"/>
     </row>
   </sheetData>

--- a/data/Database_Katalog_mi.do.ri.xlsx
+++ b/data/Database_Katalog_mi.do.ri.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\mi.do.ri_Webstore_v2.3_Promo_GitHub\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F971802-A5BE-4972-8762-AC921B371A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EAF5A60-5A2D-4CBB-9BF1-9C50CB640FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4552" uniqueCount="1390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4569" uniqueCount="1388">
   <si>
     <t>ID_PRODUK</t>
   </si>
@@ -4197,21 +4197,16 @@
   </si>
   <si>
     <t>7.7 Sale</t>
-  </si>
-  <si>
-    <t>31/08/2026</t>
-  </si>
-  <si>
-    <t>31/8/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;Rp&quot;\ #,##0"/>
     <numFmt numFmtId="166" formatCode="0&quot;%&quot;"/>
+    <numFmt numFmtId="174" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -4512,9 +4507,9 @@
     <xf numFmtId="166" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4978,11 +4973,11 @@
       <c r="Z2" s="40">
         <v>60</v>
       </c>
-      <c r="AA2" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB2" s="44" t="s">
-        <v>1389</v>
+      <c r="AA2" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB2" s="43">
+        <v>46234</v>
       </c>
       <c r="AC2" s="4" t="s">
         <v>1387</v>
@@ -5057,11 +5052,11 @@
       <c r="Z3" s="41">
         <v>60</v>
       </c>
-      <c r="AA3" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB3" s="44" t="s">
-        <v>1388</v>
+      <c r="AA3" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB3" s="43">
+        <v>46234</v>
       </c>
       <c r="AC3" s="4" t="s">
         <v>1387</v>
@@ -5136,11 +5131,11 @@
       <c r="Z4" s="41">
         <v>60</v>
       </c>
-      <c r="AA4" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB4" s="44" t="s">
-        <v>1388</v>
+      <c r="AA4" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB4" s="43">
+        <v>46234</v>
       </c>
       <c r="AC4" s="4" t="s">
         <v>1387</v>
@@ -5215,11 +5210,11 @@
       <c r="Z5" s="41">
         <v>60</v>
       </c>
-      <c r="AA5" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB5" s="44" t="s">
-        <v>1388</v>
+      <c r="AA5" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB5" s="43">
+        <v>46234</v>
       </c>
       <c r="AC5" s="4" t="s">
         <v>1387</v>
@@ -5292,11 +5287,11 @@
       <c r="Z6" s="41">
         <v>60</v>
       </c>
-      <c r="AA6" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB6" s="44" t="s">
-        <v>1388</v>
+      <c r="AA6" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB6" s="43">
+        <v>46234</v>
       </c>
       <c r="AC6" s="4" t="s">
         <v>1387</v>
@@ -5369,11 +5364,11 @@
       <c r="Z7" s="41">
         <v>60</v>
       </c>
-      <c r="AA7" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB7" s="44" t="s">
-        <v>1388</v>
+      <c r="AA7" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB7" s="43">
+        <v>46234</v>
       </c>
       <c r="AC7" s="4" t="s">
         <v>1387</v>
@@ -5448,11 +5443,11 @@
       <c r="Z8" s="41">
         <v>60</v>
       </c>
-      <c r="AA8" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB8" s="44" t="s">
-        <v>1388</v>
+      <c r="AA8" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB8" s="43">
+        <v>46234</v>
       </c>
       <c r="AC8" s="4" t="s">
         <v>1387</v>
@@ -5527,11 +5522,11 @@
       <c r="Z9" s="41">
         <v>60</v>
       </c>
-      <c r="AA9" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB9" s="44" t="s">
-        <v>1388</v>
+      <c r="AA9" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB9" s="43">
+        <v>46234</v>
       </c>
       <c r="AC9" s="4" t="s">
         <v>1387</v>
@@ -5606,11 +5601,11 @@
       <c r="Z10" s="41">
         <v>60</v>
       </c>
-      <c r="AA10" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB10" s="44" t="s">
-        <v>1388</v>
+      <c r="AA10" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB10" s="43">
+        <v>46234</v>
       </c>
       <c r="AC10" s="4" t="s">
         <v>1387</v>
@@ -5683,11 +5678,11 @@
       <c r="Z11" s="41">
         <v>60</v>
       </c>
-      <c r="AA11" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB11" s="44" t="s">
-        <v>1388</v>
+      <c r="AA11" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB11" s="43">
+        <v>46234</v>
       </c>
       <c r="AC11" s="4" t="s">
         <v>1387</v>
@@ -5760,11 +5755,11 @@
       <c r="Z12" s="41">
         <v>60</v>
       </c>
-      <c r="AA12" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB12" s="44" t="s">
-        <v>1388</v>
+      <c r="AA12" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB12" s="43">
+        <v>46234</v>
       </c>
       <c r="AC12" s="4" t="s">
         <v>1387</v>
@@ -5837,11 +5832,11 @@
       <c r="Z13" s="41">
         <v>60</v>
       </c>
-      <c r="AA13" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB13" s="44" t="s">
-        <v>1388</v>
+      <c r="AA13" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB13" s="43">
+        <v>46234</v>
       </c>
       <c r="AC13" s="4" t="s">
         <v>1387</v>
@@ -5914,11 +5909,11 @@
       <c r="Z14" s="41">
         <v>60</v>
       </c>
-      <c r="AA14" s="44">
-        <v>46030</v>
-      </c>
-      <c r="AB14" s="44" t="s">
-        <v>1388</v>
+      <c r="AA14" s="43">
+        <v>46204</v>
+      </c>
+      <c r="AB14" s="43">
+        <v>46234</v>
       </c>
       <c r="AC14" s="4" t="s">
         <v>1387</v>
@@ -5984,14 +5979,20 @@
       </c>
       <c r="X15" s="10"/>
       <c r="Y15" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z15" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="43"/>
-      <c r="AB15" s="43"/>
-      <c r="AC15" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA15" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB15" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC15" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="16" spans="1:29">
       <c r="A16" s="20" t="s">
@@ -6057,14 +6058,20 @@
       </c>
       <c r="X16" s="10"/>
       <c r="Y16" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z16" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="43"/>
-      <c r="AB16" s="43"/>
-      <c r="AC16" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA16" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB16" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC16" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="17" spans="1:29">
       <c r="A17" s="20" t="s">
@@ -6128,14 +6135,20 @@
       </c>
       <c r="X17" s="10"/>
       <c r="Y17" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z17" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="43"/>
-      <c r="AB17" s="43"/>
-      <c r="AC17" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA17" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB17" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC17" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="18" spans="1:29">
       <c r="A18" s="20" t="s">
@@ -6199,14 +6212,20 @@
       </c>
       <c r="X18" s="10"/>
       <c r="Y18" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z18" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="43"/>
-      <c r="AB18" s="43"/>
-      <c r="AC18" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA18" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB18" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC18" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="19" spans="1:29">
       <c r="A19" s="20" t="s">
@@ -6270,14 +6289,20 @@
       </c>
       <c r="X19" s="10"/>
       <c r="Y19" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z19" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="43"/>
-      <c r="AB19" s="43"/>
-      <c r="AC19" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA19" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB19" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC19" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="20" spans="1:29">
       <c r="A20" s="20" t="s">
@@ -6341,14 +6366,20 @@
       </c>
       <c r="X20" s="10"/>
       <c r="Y20" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z20" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="43"/>
-      <c r="AB20" s="43"/>
-      <c r="AC20" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA20" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB20" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC20" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="21" spans="1:29">
       <c r="A21" s="20" t="s">
@@ -6412,14 +6443,20 @@
       </c>
       <c r="X21" s="10"/>
       <c r="Y21" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z21" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="43"/>
-      <c r="AB21" s="43"/>
-      <c r="AC21" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA21" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB21" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC21" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="22" spans="1:29">
       <c r="A22" s="20" t="s">
@@ -6483,14 +6520,20 @@
       </c>
       <c r="X22" s="10"/>
       <c r="Y22" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z22" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="43"/>
-      <c r="AB22" s="43"/>
-      <c r="AC22" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA22" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB22" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC22" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="23" spans="1:29">
       <c r="A23" s="20" t="s">
@@ -6554,14 +6597,20 @@
       </c>
       <c r="X23" s="10"/>
       <c r="Y23" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z23" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="43"/>
-      <c r="AB23" s="43"/>
-      <c r="AC23" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA23" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB23" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC23" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="24" spans="1:29">
       <c r="A24" s="20" t="s">
@@ -6625,14 +6674,20 @@
       </c>
       <c r="X24" s="10"/>
       <c r="Y24" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z24" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="43"/>
-      <c r="AB24" s="43"/>
-      <c r="AC24" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA24" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB24" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC24" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="25" spans="1:29">
       <c r="A25" s="20" t="s">
@@ -6696,14 +6751,20 @@
       </c>
       <c r="X25" s="10"/>
       <c r="Y25" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z25" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="43"/>
-      <c r="AB25" s="43"/>
-      <c r="AC25" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA25" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB25" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC25" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="26" spans="1:29">
       <c r="A26" s="20" t="s">
@@ -6769,14 +6830,20 @@
       </c>
       <c r="X26" s="10"/>
       <c r="Y26" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z26" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="43"/>
-      <c r="AB26" s="43"/>
-      <c r="AC26" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA26" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB26" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC26" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="27" spans="1:29">
       <c r="A27" s="20" t="s">
@@ -6840,14 +6907,20 @@
       </c>
       <c r="X27" s="10"/>
       <c r="Y27" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z27" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="43"/>
-      <c r="AB27" s="43"/>
-      <c r="AC27" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA27" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB27" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC27" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="28" spans="1:29">
       <c r="A28" s="20" t="s">
@@ -6911,14 +6984,20 @@
       </c>
       <c r="X28" s="10"/>
       <c r="Y28" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z28" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="43"/>
-      <c r="AB28" s="43"/>
-      <c r="AC28" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA28" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB28" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC28" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="29" spans="1:29">
       <c r="A29" s="20" t="s">
@@ -6984,14 +7063,20 @@
       </c>
       <c r="X29" s="10"/>
       <c r="Y29" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z29" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="43"/>
-      <c r="AB29" s="43"/>
-      <c r="AC29" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA29" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB29" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC29" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="30" spans="1:29">
       <c r="A30" s="20" t="s">
@@ -7055,14 +7140,20 @@
       </c>
       <c r="X30" s="10"/>
       <c r="Y30" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z30" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="43"/>
-      <c r="AB30" s="43"/>
-      <c r="AC30" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA30" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB30" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC30" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="31" spans="1:29">
       <c r="A31" s="20" t="s">
@@ -7128,14 +7219,20 @@
       </c>
       <c r="X31" s="10"/>
       <c r="Y31" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z31" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="43"/>
-      <c r="AB31" s="43"/>
-      <c r="AC31" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA31" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB31" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC31" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="32" spans="1:29">
       <c r="A32" s="20" t="s">
@@ -7199,14 +7296,20 @@
       </c>
       <c r="X32" s="10"/>
       <c r="Y32" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z32" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="43"/>
-      <c r="AB32" s="43"/>
-      <c r="AC32" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA32" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB32" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC32" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="33" spans="1:29">
       <c r="A33" s="20" t="s">
@@ -7270,14 +7373,20 @@
       </c>
       <c r="X33" s="10"/>
       <c r="Y33" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z33" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="43"/>
-      <c r="AB33" s="43"/>
-      <c r="AC33" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA33" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB33" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC33" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="34" spans="1:29" ht="28">
       <c r="A34" s="20" t="s">
@@ -7341,14 +7450,20 @@
       </c>
       <c r="X34" s="10"/>
       <c r="Y34" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z34" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="43"/>
-      <c r="AB34" s="43"/>
-      <c r="AC34" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA34" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB34" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC34" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="35" spans="1:29">
       <c r="A35" s="20" t="s">
@@ -7412,14 +7527,20 @@
       </c>
       <c r="X35" s="10"/>
       <c r="Y35" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z35" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="43"/>
-      <c r="AB35" s="43"/>
-      <c r="AC35" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA35" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB35" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC35" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="36" spans="1:29">
       <c r="A36" s="20" t="s">
@@ -7483,14 +7604,20 @@
       </c>
       <c r="X36" s="10"/>
       <c r="Y36" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z36" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="43"/>
-      <c r="AB36" s="43"/>
-      <c r="AC36" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA36" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB36" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC36" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="37" spans="1:29">
       <c r="A37" s="20" t="s">
@@ -7554,14 +7681,20 @@
       </c>
       <c r="X37" s="10"/>
       <c r="Y37" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z37" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA37" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB37" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC37" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="38" spans="1:29">
       <c r="A38" s="20" t="s">
@@ -7627,14 +7760,20 @@
       </c>
       <c r="X38" s="10"/>
       <c r="Y38" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z38" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="43"/>
-      <c r="AB38" s="43"/>
-      <c r="AC38" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA38" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB38" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC38" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="39" spans="1:29">
       <c r="A39" s="20" t="s">
@@ -7698,14 +7837,20 @@
       </c>
       <c r="X39" s="10"/>
       <c r="Y39" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z39" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="43"/>
-      <c r="AB39" s="43"/>
-      <c r="AC39" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA39" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB39" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC39" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="40" spans="1:29">
       <c r="A40" s="20" t="s">
@@ -7769,14 +7914,20 @@
       </c>
       <c r="X40" s="10"/>
       <c r="Y40" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z40" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="43"/>
-      <c r="AB40" s="43"/>
-      <c r="AC40" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA40" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB40" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC40" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="41" spans="1:29">
       <c r="A41" s="20" t="s">
@@ -7840,14 +7991,20 @@
       </c>
       <c r="X41" s="10"/>
       <c r="Y41" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z41" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="43"/>
-      <c r="AB41" s="43"/>
-      <c r="AC41" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA41" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB41" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC41" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="42" spans="1:29">
       <c r="A42" s="20" t="s">
@@ -7911,14 +8068,20 @@
       </c>
       <c r="X42" s="10"/>
       <c r="Y42" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z42" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="43"/>
-      <c r="AB42" s="43"/>
-      <c r="AC42" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA42" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB42" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC42" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="43" spans="1:29">
       <c r="A43" s="20" t="s">
@@ -7982,14 +8145,20 @@
       </c>
       <c r="X43" s="10"/>
       <c r="Y43" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z43" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="43"/>
-      <c r="AB43" s="43"/>
-      <c r="AC43" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA43" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB43" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC43" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="44" spans="1:29">
       <c r="A44" s="20" t="s">
@@ -8053,14 +8222,20 @@
       </c>
       <c r="X44" s="10"/>
       <c r="Y44" s="38" t="s">
-        <v>39</v>
+        <v>1386</v>
       </c>
       <c r="Z44" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="43"/>
-      <c r="AB44" s="43"/>
-      <c r="AC44" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="AA44" s="44">
+        <v>46204</v>
+      </c>
+      <c r="AB44" s="43">
+        <v>46234</v>
+      </c>
+      <c r="AC44" s="4" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="45" spans="1:29">
       <c r="A45" s="20" t="s">
@@ -8129,8 +8304,8 @@
       <c r="Z45" s="41">
         <v>0</v>
       </c>
-      <c r="AA45" s="43"/>
-      <c r="AB45" s="43"/>
+      <c r="AA45" s="44"/>
+      <c r="AB45" s="44"/>
       <c r="AC45" s="5"/>
     </row>
     <row r="46" spans="1:29">
@@ -8200,8 +8375,8 @@
       <c r="Z46" s="41">
         <v>0</v>
       </c>
-      <c r="AA46" s="43"/>
-      <c r="AB46" s="43"/>
+      <c r="AA46" s="44"/>
+      <c r="AB46" s="44"/>
       <c r="AC46" s="5"/>
     </row>
     <row r="47" spans="1:29">
@@ -8269,8 +8444,8 @@
       <c r="Z47" s="41">
         <v>0</v>
       </c>
-      <c r="AA47" s="43"/>
-      <c r="AB47" s="43"/>
+      <c r="AA47" s="44"/>
+      <c r="AB47" s="44"/>
       <c r="AC47" s="5"/>
     </row>
     <row r="48" spans="1:29">
@@ -8340,8 +8515,8 @@
       <c r="Z48" s="41">
         <v>0</v>
       </c>
-      <c r="AA48" s="43"/>
-      <c r="AB48" s="43"/>
+      <c r="AA48" s="44"/>
+      <c r="AB48" s="44"/>
       <c r="AC48" s="5"/>
     </row>
     <row r="49" spans="1:29">
@@ -8409,8 +8584,8 @@
       <c r="Z49" s="41">
         <v>0</v>
       </c>
-      <c r="AA49" s="43"/>
-      <c r="AB49" s="43"/>
+      <c r="AA49" s="44"/>
+      <c r="AB49" s="44"/>
       <c r="AC49" s="5"/>
     </row>
     <row r="50" spans="1:29">
@@ -8480,8 +8655,8 @@
       <c r="Z50" s="41">
         <v>0</v>
       </c>
-      <c r="AA50" s="43"/>
-      <c r="AB50" s="43"/>
+      <c r="AA50" s="44"/>
+      <c r="AB50" s="44"/>
       <c r="AC50" s="5"/>
     </row>
     <row r="51" spans="1:29">
@@ -8551,8 +8726,8 @@
       <c r="Z51" s="41">
         <v>0</v>
       </c>
-      <c r="AA51" s="43"/>
-      <c r="AB51" s="43"/>
+      <c r="AA51" s="44"/>
+      <c r="AB51" s="44"/>
       <c r="AC51" s="5"/>
     </row>
     <row r="52" spans="1:29">
@@ -8620,8 +8795,8 @@
       <c r="Z52" s="41">
         <v>0</v>
       </c>
-      <c r="AA52" s="43"/>
-      <c r="AB52" s="43"/>
+      <c r="AA52" s="44"/>
+      <c r="AB52" s="44"/>
       <c r="AC52" s="5"/>
     </row>
     <row r="53" spans="1:29">
@@ -8689,8 +8864,8 @@
       <c r="Z53" s="41">
         <v>0</v>
       </c>
-      <c r="AA53" s="43"/>
-      <c r="AB53" s="43"/>
+      <c r="AA53" s="44"/>
+      <c r="AB53" s="44"/>
       <c r="AC53" s="5"/>
     </row>
     <row r="54" spans="1:29">
@@ -8760,8 +8935,8 @@
       <c r="Z54" s="41">
         <v>0</v>
       </c>
-      <c r="AA54" s="43"/>
-      <c r="AB54" s="43"/>
+      <c r="AA54" s="44"/>
+      <c r="AB54" s="44"/>
       <c r="AC54" s="5"/>
     </row>
     <row r="55" spans="1:29">
@@ -8829,8 +9004,8 @@
       <c r="Z55" s="41">
         <v>0</v>
       </c>
-      <c r="AA55" s="43"/>
-      <c r="AB55" s="43"/>
+      <c r="AA55" s="44"/>
+      <c r="AB55" s="44"/>
       <c r="AC55" s="5"/>
     </row>
     <row r="56" spans="1:29" ht="28">
@@ -8898,8 +9073,8 @@
       <c r="Z56" s="41">
         <v>0</v>
       </c>
-      <c r="AA56" s="43"/>
-      <c r="AB56" s="43"/>
+      <c r="AA56" s="44"/>
+      <c r="AB56" s="44"/>
       <c r="AC56" s="5"/>
     </row>
     <row r="57" spans="1:29">
@@ -8971,8 +9146,8 @@
       <c r="Z57" s="41">
         <v>0</v>
       </c>
-      <c r="AA57" s="43"/>
-      <c r="AB57" s="43"/>
+      <c r="AA57" s="44"/>
+      <c r="AB57" s="44"/>
       <c r="AC57" s="5"/>
     </row>
     <row r="58" spans="1:29">
@@ -9042,8 +9217,8 @@
       <c r="Z58" s="41">
         <v>0</v>
       </c>
-      <c r="AA58" s="43"/>
-      <c r="AB58" s="43"/>
+      <c r="AA58" s="44"/>
+      <c r="AB58" s="44"/>
       <c r="AC58" s="5"/>
     </row>
     <row r="59" spans="1:29">
@@ -9113,8 +9288,8 @@
       <c r="Z59" s="41">
         <v>0</v>
       </c>
-      <c r="AA59" s="43"/>
-      <c r="AB59" s="43"/>
+      <c r="AA59" s="44"/>
+      <c r="AB59" s="44"/>
       <c r="AC59" s="5"/>
     </row>
     <row r="60" spans="1:29">
@@ -9184,8 +9359,8 @@
       <c r="Z60" s="41">
         <v>0</v>
       </c>
-      <c r="AA60" s="43"/>
-      <c r="AB60" s="43"/>
+      <c r="AA60" s="44"/>
+      <c r="AB60" s="44"/>
       <c r="AC60" s="5"/>
     </row>
     <row r="61" spans="1:29">
@@ -9255,8 +9430,8 @@
       <c r="Z61" s="41">
         <v>0</v>
       </c>
-      <c r="AA61" s="43"/>
-      <c r="AB61" s="43"/>
+      <c r="AA61" s="44"/>
+      <c r="AB61" s="44"/>
       <c r="AC61" s="5"/>
     </row>
     <row r="62" spans="1:29">
@@ -9324,8 +9499,8 @@
       <c r="Z62" s="41">
         <v>0</v>
       </c>
-      <c r="AA62" s="43"/>
-      <c r="AB62" s="43"/>
+      <c r="AA62" s="44"/>
+      <c r="AB62" s="44"/>
       <c r="AC62" s="5"/>
     </row>
     <row r="63" spans="1:29">
@@ -9393,8 +9568,8 @@
       <c r="Z63" s="41">
         <v>0</v>
       </c>
-      <c r="AA63" s="43"/>
-      <c r="AB63" s="43"/>
+      <c r="AA63" s="44"/>
+      <c r="AB63" s="44"/>
       <c r="AC63" s="5"/>
     </row>
     <row r="64" spans="1:29">
@@ -9464,8 +9639,8 @@
       <c r="Z64" s="41">
         <v>0</v>
       </c>
-      <c r="AA64" s="43"/>
-      <c r="AB64" s="43"/>
+      <c r="AA64" s="44"/>
+      <c r="AB64" s="44"/>
       <c r="AC64" s="5"/>
     </row>
     <row r="65" spans="1:29">
@@ -9533,8 +9708,8 @@
       <c r="Z65" s="41">
         <v>0</v>
       </c>
-      <c r="AA65" s="43"/>
-      <c r="AB65" s="43"/>
+      <c r="AA65" s="44"/>
+      <c r="AB65" s="44"/>
       <c r="AC65" s="5"/>
     </row>
     <row r="66" spans="1:29">
@@ -9602,8 +9777,8 @@
       <c r="Z66" s="41">
         <v>0</v>
       </c>
-      <c r="AA66" s="43"/>
-      <c r="AB66" s="43"/>
+      <c r="AA66" s="44"/>
+      <c r="AB66" s="44"/>
       <c r="AC66" s="5"/>
     </row>
     <row r="67" spans="1:29">
@@ -9673,8 +9848,8 @@
       <c r="Z67" s="41">
         <v>0</v>
       </c>
-      <c r="AA67" s="43"/>
-      <c r="AB67" s="43"/>
+      <c r="AA67" s="44"/>
+      <c r="AB67" s="44"/>
       <c r="AC67" s="5"/>
     </row>
     <row r="68" spans="1:29">
@@ -9744,8 +9919,8 @@
       <c r="Z68" s="41">
         <v>0</v>
       </c>
-      <c r="AA68" s="43"/>
-      <c r="AB68" s="43"/>
+      <c r="AA68" s="44"/>
+      <c r="AB68" s="44"/>
       <c r="AC68" s="5"/>
     </row>
     <row r="69" spans="1:29">
@@ -9815,8 +9990,8 @@
       <c r="Z69" s="41">
         <v>0</v>
       </c>
-      <c r="AA69" s="43"/>
-      <c r="AB69" s="43"/>
+      <c r="AA69" s="44"/>
+      <c r="AB69" s="44"/>
       <c r="AC69" s="5"/>
     </row>
     <row r="70" spans="1:29">
@@ -9886,8 +10061,8 @@
       <c r="Z70" s="41">
         <v>0</v>
       </c>
-      <c r="AA70" s="43"/>
-      <c r="AB70" s="43"/>
+      <c r="AA70" s="44"/>
+      <c r="AB70" s="44"/>
       <c r="AC70" s="5"/>
     </row>
     <row r="71" spans="1:29">
@@ -9957,8 +10132,8 @@
       <c r="Z71" s="41">
         <v>0</v>
       </c>
-      <c r="AA71" s="43"/>
-      <c r="AB71" s="43"/>
+      <c r="AA71" s="44"/>
+      <c r="AB71" s="44"/>
       <c r="AC71" s="5"/>
     </row>
     <row r="72" spans="1:29">
@@ -10026,8 +10201,8 @@
       <c r="Z72" s="41">
         <v>0</v>
       </c>
-      <c r="AA72" s="43"/>
-      <c r="AB72" s="43"/>
+      <c r="AA72" s="44"/>
+      <c r="AB72" s="44"/>
       <c r="AC72" s="5"/>
     </row>
     <row r="73" spans="1:29">
@@ -10097,8 +10272,8 @@
       <c r="Z73" s="41">
         <v>0</v>
       </c>
-      <c r="AA73" s="43"/>
-      <c r="AB73" s="43"/>
+      <c r="AA73" s="44"/>
+      <c r="AB73" s="44"/>
       <c r="AC73" s="5"/>
     </row>
     <row r="74" spans="1:29">
@@ -10168,8 +10343,8 @@
       <c r="Z74" s="41">
         <v>0</v>
       </c>
-      <c r="AA74" s="43"/>
-      <c r="AB74" s="43"/>
+      <c r="AA74" s="44"/>
+      <c r="AB74" s="44"/>
       <c r="AC74" s="5"/>
     </row>
     <row r="75" spans="1:29">
@@ -10239,8 +10414,8 @@
       <c r="Z75" s="41">
         <v>0</v>
       </c>
-      <c r="AA75" s="43"/>
-      <c r="AB75" s="43"/>
+      <c r="AA75" s="44"/>
+      <c r="AB75" s="44"/>
       <c r="AC75" s="5"/>
     </row>
     <row r="76" spans="1:29">
@@ -10310,8 +10485,8 @@
       <c r="Z76" s="41">
         <v>0</v>
       </c>
-      <c r="AA76" s="43"/>
-      <c r="AB76" s="43"/>
+      <c r="AA76" s="44"/>
+      <c r="AB76" s="44"/>
       <c r="AC76" s="5"/>
     </row>
     <row r="77" spans="1:29">
@@ -10379,8 +10554,8 @@
       <c r="Z77" s="41">
         <v>0</v>
       </c>
-      <c r="AA77" s="43"/>
-      <c r="AB77" s="43"/>
+      <c r="AA77" s="44"/>
+      <c r="AB77" s="44"/>
       <c r="AC77" s="5"/>
     </row>
     <row r="78" spans="1:29">
@@ -10448,8 +10623,8 @@
       <c r="Z78" s="41">
         <v>0</v>
       </c>
-      <c r="AA78" s="43"/>
-      <c r="AB78" s="43"/>
+      <c r="AA78" s="44"/>
+      <c r="AB78" s="44"/>
       <c r="AC78" s="5"/>
     </row>
     <row r="79" spans="1:29">
@@ -10517,8 +10692,8 @@
       <c r="Z79" s="41">
         <v>0</v>
       </c>
-      <c r="AA79" s="43"/>
-      <c r="AB79" s="43"/>
+      <c r="AA79" s="44"/>
+      <c r="AB79" s="44"/>
       <c r="AC79" s="5"/>
     </row>
     <row r="80" spans="1:29">
@@ -10588,8 +10763,8 @@
       <c r="Z80" s="41">
         <v>0</v>
       </c>
-      <c r="AA80" s="43"/>
-      <c r="AB80" s="43"/>
+      <c r="AA80" s="44"/>
+      <c r="AB80" s="44"/>
       <c r="AC80" s="5"/>
     </row>
     <row r="81" spans="1:29">
@@ -10657,8 +10832,8 @@
       <c r="Z81" s="41">
         <v>0</v>
       </c>
-      <c r="AA81" s="43"/>
-      <c r="AB81" s="43"/>
+      <c r="AA81" s="44"/>
+      <c r="AB81" s="44"/>
       <c r="AC81" s="5"/>
     </row>
     <row r="82" spans="1:29">
@@ -10726,8 +10901,8 @@
       <c r="Z82" s="41">
         <v>0</v>
       </c>
-      <c r="AA82" s="43"/>
-      <c r="AB82" s="43"/>
+      <c r="AA82" s="44"/>
+      <c r="AB82" s="44"/>
       <c r="AC82" s="5"/>
     </row>
     <row r="83" spans="1:29">
@@ -10795,8 +10970,8 @@
       <c r="Z83" s="41">
         <v>0</v>
       </c>
-      <c r="AA83" s="43"/>
-      <c r="AB83" s="43"/>
+      <c r="AA83" s="44"/>
+      <c r="AB83" s="44"/>
       <c r="AC83" s="5"/>
     </row>
     <row r="84" spans="1:29">
@@ -10866,8 +11041,8 @@
       <c r="Z84" s="41">
         <v>0</v>
       </c>
-      <c r="AA84" s="43"/>
-      <c r="AB84" s="43"/>
+      <c r="AA84" s="44"/>
+      <c r="AB84" s="44"/>
       <c r="AC84" s="5"/>
     </row>
     <row r="85" spans="1:29">
@@ -10937,8 +11112,8 @@
       <c r="Z85" s="41">
         <v>0</v>
       </c>
-      <c r="AA85" s="43"/>
-      <c r="AB85" s="43"/>
+      <c r="AA85" s="44"/>
+      <c r="AB85" s="44"/>
       <c r="AC85" s="5"/>
     </row>
     <row r="86" spans="1:29">
@@ -11006,8 +11181,8 @@
       <c r="Z86" s="41">
         <v>0</v>
       </c>
-      <c r="AA86" s="43"/>
-      <c r="AB86" s="43"/>
+      <c r="AA86" s="44"/>
+      <c r="AB86" s="44"/>
       <c r="AC86" s="5"/>
     </row>
     <row r="87" spans="1:29">
@@ -11077,8 +11252,8 @@
       <c r="Z87" s="41">
         <v>0</v>
       </c>
-      <c r="AA87" s="43"/>
-      <c r="AB87" s="43"/>
+      <c r="AA87" s="44"/>
+      <c r="AB87" s="44"/>
       <c r="AC87" s="5"/>
     </row>
     <row r="88" spans="1:29">
@@ -11148,8 +11323,8 @@
       <c r="Z88" s="41">
         <v>0</v>
       </c>
-      <c r="AA88" s="43"/>
-      <c r="AB88" s="43"/>
+      <c r="AA88" s="44"/>
+      <c r="AB88" s="44"/>
       <c r="AC88" s="5"/>
     </row>
     <row r="89" spans="1:29">
@@ -11219,8 +11394,8 @@
       <c r="Z89" s="41">
         <v>0</v>
       </c>
-      <c r="AA89" s="43"/>
-      <c r="AB89" s="43"/>
+      <c r="AA89" s="44"/>
+      <c r="AB89" s="44"/>
       <c r="AC89" s="5"/>
     </row>
     <row r="90" spans="1:29">
@@ -11292,8 +11467,8 @@
       <c r="Z90" s="41">
         <v>0</v>
       </c>
-      <c r="AA90" s="43"/>
-      <c r="AB90" s="43"/>
+      <c r="AA90" s="44"/>
+      <c r="AB90" s="44"/>
       <c r="AC90" s="5"/>
     </row>
     <row r="91" spans="1:29">
@@ -11365,8 +11540,8 @@
       <c r="Z91" s="41">
         <v>0</v>
       </c>
-      <c r="AA91" s="43"/>
-      <c r="AB91" s="43"/>
+      <c r="AA91" s="44"/>
+      <c r="AB91" s="44"/>
       <c r="AC91" s="5"/>
     </row>
     <row r="92" spans="1:29">
@@ -11436,8 +11611,8 @@
       <c r="Z92" s="41">
         <v>0</v>
       </c>
-      <c r="AA92" s="43"/>
-      <c r="AB92" s="43"/>
+      <c r="AA92" s="44"/>
+      <c r="AB92" s="44"/>
       <c r="AC92" s="5"/>
     </row>
     <row r="93" spans="1:29">
@@ -11507,8 +11682,8 @@
       <c r="Z93" s="41">
         <v>0</v>
       </c>
-      <c r="AA93" s="43"/>
-      <c r="AB93" s="43"/>
+      <c r="AA93" s="44"/>
+      <c r="AB93" s="44"/>
       <c r="AC93" s="5"/>
     </row>
     <row r="94" spans="1:29">
@@ -11578,8 +11753,8 @@
       <c r="Z94" s="41">
         <v>0</v>
       </c>
-      <c r="AA94" s="43"/>
-      <c r="AB94" s="43"/>
+      <c r="AA94" s="44"/>
+      <c r="AB94" s="44"/>
       <c r="AC94" s="5"/>
     </row>
     <row r="95" spans="1:29">
@@ -11651,8 +11826,8 @@
       <c r="Z95" s="41">
         <v>0</v>
       </c>
-      <c r="AA95" s="43"/>
-      <c r="AB95" s="43"/>
+      <c r="AA95" s="44"/>
+      <c r="AB95" s="44"/>
       <c r="AC95" s="5"/>
     </row>
     <row r="96" spans="1:29">
@@ -11724,8 +11899,8 @@
       <c r="Z96" s="41">
         <v>0</v>
       </c>
-      <c r="AA96" s="43"/>
-      <c r="AB96" s="43"/>
+      <c r="AA96" s="44"/>
+      <c r="AB96" s="44"/>
       <c r="AC96" s="5"/>
     </row>
     <row r="97" spans="1:29">
@@ -11797,8 +11972,8 @@
       <c r="Z97" s="41">
         <v>0</v>
       </c>
-      <c r="AA97" s="43"/>
-      <c r="AB97" s="43"/>
+      <c r="AA97" s="44"/>
+      <c r="AB97" s="44"/>
       <c r="AC97" s="5"/>
     </row>
     <row r="98" spans="1:29">
@@ -11870,8 +12045,8 @@
       <c r="Z98" s="41">
         <v>0</v>
       </c>
-      <c r="AA98" s="43"/>
-      <c r="AB98" s="43"/>
+      <c r="AA98" s="44"/>
+      <c r="AB98" s="44"/>
       <c r="AC98" s="5"/>
     </row>
     <row r="99" spans="1:29">
@@ -11939,8 +12114,8 @@
       <c r="Z99" s="41">
         <v>0</v>
       </c>
-      <c r="AA99" s="43"/>
-      <c r="AB99" s="43"/>
+      <c r="AA99" s="44"/>
+      <c r="AB99" s="44"/>
       <c r="AC99" s="5"/>
     </row>
     <row r="100" spans="1:29">
@@ -12010,8 +12185,8 @@
       <c r="Z100" s="41">
         <v>0</v>
       </c>
-      <c r="AA100" s="43"/>
-      <c r="AB100" s="43"/>
+      <c r="AA100" s="44"/>
+      <c r="AB100" s="44"/>
       <c r="AC100" s="5"/>
     </row>
     <row r="101" spans="1:29">
@@ -12081,8 +12256,8 @@
       <c r="Z101" s="41">
         <v>0</v>
       </c>
-      <c r="AA101" s="43"/>
-      <c r="AB101" s="43"/>
+      <c r="AA101" s="44"/>
+      <c r="AB101" s="44"/>
       <c r="AC101" s="5"/>
     </row>
     <row r="102" spans="1:29">
@@ -12152,8 +12327,8 @@
       <c r="Z102" s="41">
         <v>0</v>
       </c>
-      <c r="AA102" s="43"/>
-      <c r="AB102" s="43"/>
+      <c r="AA102" s="44"/>
+      <c r="AB102" s="44"/>
       <c r="AC102" s="5"/>
     </row>
     <row r="103" spans="1:29">
@@ -12223,8 +12398,8 @@
       <c r="Z103" s="41">
         <v>0</v>
       </c>
-      <c r="AA103" s="43"/>
-      <c r="AB103" s="43"/>
+      <c r="AA103" s="44"/>
+      <c r="AB103" s="44"/>
       <c r="AC103" s="5"/>
     </row>
     <row r="104" spans="1:29">
@@ -12292,8 +12467,8 @@
       <c r="Z104" s="41">
         <v>0</v>
       </c>
-      <c r="AA104" s="43"/>
-      <c r="AB104" s="43"/>
+      <c r="AA104" s="44"/>
+      <c r="AB104" s="44"/>
       <c r="AC104" s="5"/>
     </row>
     <row r="105" spans="1:29">
@@ -12361,8 +12536,8 @@
       <c r="Z105" s="41">
         <v>0</v>
       </c>
-      <c r="AA105" s="43"/>
-      <c r="AB105" s="43"/>
+      <c r="AA105" s="44"/>
+      <c r="AB105" s="44"/>
       <c r="AC105" s="5"/>
     </row>
     <row r="106" spans="1:29">
@@ -12430,8 +12605,8 @@
       <c r="Z106" s="41">
         <v>0</v>
       </c>
-      <c r="AA106" s="43"/>
-      <c r="AB106" s="43"/>
+      <c r="AA106" s="44"/>
+      <c r="AB106" s="44"/>
       <c r="AC106" s="5"/>
     </row>
     <row r="107" spans="1:29">
@@ -12499,8 +12674,8 @@
       <c r="Z107" s="41">
         <v>0</v>
       </c>
-      <c r="AA107" s="43"/>
-      <c r="AB107" s="43"/>
+      <c r="AA107" s="44"/>
+      <c r="AB107" s="44"/>
       <c r="AC107" s="5"/>
     </row>
     <row r="108" spans="1:29">
@@ -12568,8 +12743,8 @@
       <c r="Z108" s="41">
         <v>0</v>
       </c>
-      <c r="AA108" s="43"/>
-      <c r="AB108" s="43"/>
+      <c r="AA108" s="44"/>
+      <c r="AB108" s="44"/>
       <c r="AC108" s="5"/>
     </row>
     <row r="109" spans="1:29">
@@ -12637,8 +12812,8 @@
       <c r="Z109" s="41">
         <v>0</v>
       </c>
-      <c r="AA109" s="43"/>
-      <c r="AB109" s="43"/>
+      <c r="AA109" s="44"/>
+      <c r="AB109" s="44"/>
       <c r="AC109" s="5"/>
     </row>
     <row r="110" spans="1:29">
@@ -12708,8 +12883,8 @@
       <c r="Z110" s="41">
         <v>0</v>
       </c>
-      <c r="AA110" s="43"/>
-      <c r="AB110" s="43"/>
+      <c r="AA110" s="44"/>
+      <c r="AB110" s="44"/>
       <c r="AC110" s="5"/>
     </row>
     <row r="111" spans="1:29">
@@ -12777,8 +12952,8 @@
       <c r="Z111" s="41">
         <v>0</v>
       </c>
-      <c r="AA111" s="43"/>
-      <c r="AB111" s="43"/>
+      <c r="AA111" s="44"/>
+      <c r="AB111" s="44"/>
       <c r="AC111" s="5"/>
     </row>
     <row r="112" spans="1:29">
@@ -12846,8 +13021,8 @@
       <c r="Z112" s="41">
         <v>0</v>
       </c>
-      <c r="AA112" s="43"/>
-      <c r="AB112" s="43"/>
+      <c r="AA112" s="44"/>
+      <c r="AB112" s="44"/>
       <c r="AC112" s="5"/>
     </row>
     <row r="113" spans="1:29">
@@ -12917,8 +13092,8 @@
       <c r="Z113" s="41">
         <v>0</v>
       </c>
-      <c r="AA113" s="43"/>
-      <c r="AB113" s="43"/>
+      <c r="AA113" s="44"/>
+      <c r="AB113" s="44"/>
       <c r="AC113" s="5"/>
     </row>
     <row r="114" spans="1:29">
@@ -12986,8 +13161,8 @@
       <c r="Z114" s="41">
         <v>0</v>
       </c>
-      <c r="AA114" s="43"/>
-      <c r="AB114" s="43"/>
+      <c r="AA114" s="44"/>
+      <c r="AB114" s="44"/>
       <c r="AC114" s="5"/>
     </row>
     <row r="115" spans="1:29">
@@ -13055,8 +13230,8 @@
       <c r="Z115" s="41">
         <v>0</v>
       </c>
-      <c r="AA115" s="43"/>
-      <c r="AB115" s="43"/>
+      <c r="AA115" s="44"/>
+      <c r="AB115" s="44"/>
       <c r="AC115" s="5"/>
     </row>
     <row r="116" spans="1:29">
@@ -13124,8 +13299,8 @@
       <c r="Z116" s="41">
         <v>0</v>
       </c>
-      <c r="AA116" s="43"/>
-      <c r="AB116" s="43"/>
+      <c r="AA116" s="44"/>
+      <c r="AB116" s="44"/>
       <c r="AC116" s="5"/>
     </row>
     <row r="117" spans="1:29">
@@ -13195,8 +13370,8 @@
       <c r="Z117" s="41">
         <v>0</v>
       </c>
-      <c r="AA117" s="43"/>
-      <c r="AB117" s="43"/>
+      <c r="AA117" s="44"/>
+      <c r="AB117" s="44"/>
       <c r="AC117" s="5"/>
     </row>
     <row r="118" spans="1:29">
@@ -13264,8 +13439,8 @@
       <c r="Z118" s="41">
         <v>0</v>
       </c>
-      <c r="AA118" s="43"/>
-      <c r="AB118" s="43"/>
+      <c r="AA118" s="44"/>
+      <c r="AB118" s="44"/>
       <c r="AC118" s="5"/>
     </row>
     <row r="119" spans="1:29">
@@ -13333,8 +13508,8 @@
       <c r="Z119" s="41">
         <v>0</v>
       </c>
-      <c r="AA119" s="43"/>
-      <c r="AB119" s="43"/>
+      <c r="AA119" s="44"/>
+      <c r="AB119" s="44"/>
       <c r="AC119" s="5"/>
     </row>
     <row r="120" spans="1:29">
@@ -13402,8 +13577,8 @@
       <c r="Z120" s="41">
         <v>0</v>
       </c>
-      <c r="AA120" s="43"/>
-      <c r="AB120" s="43"/>
+      <c r="AA120" s="44"/>
+      <c r="AB120" s="44"/>
       <c r="AC120" s="5"/>
     </row>
     <row r="121" spans="1:29">
@@ -13473,8 +13648,8 @@
       <c r="Z121" s="41">
         <v>0</v>
       </c>
-      <c r="AA121" s="43"/>
-      <c r="AB121" s="43"/>
+      <c r="AA121" s="44"/>
+      <c r="AB121" s="44"/>
       <c r="AC121" s="5"/>
     </row>
     <row r="122" spans="1:29">
@@ -13544,8 +13719,8 @@
       <c r="Z122" s="41">
         <v>0</v>
       </c>
-      <c r="AA122" s="43"/>
-      <c r="AB122" s="43"/>
+      <c r="AA122" s="44"/>
+      <c r="AB122" s="44"/>
       <c r="AC122" s="5"/>
     </row>
     <row r="123" spans="1:29">
@@ -13615,8 +13790,8 @@
       <c r="Z123" s="41">
         <v>0</v>
       </c>
-      <c r="AA123" s="43"/>
-      <c r="AB123" s="43"/>
+      <c r="AA123" s="44"/>
+      <c r="AB123" s="44"/>
       <c r="AC123" s="5"/>
     </row>
     <row r="124" spans="1:29">
@@ -13686,8 +13861,8 @@
       <c r="Z124" s="41">
         <v>0</v>
       </c>
-      <c r="AA124" s="43"/>
-      <c r="AB124" s="43"/>
+      <c r="AA124" s="44"/>
+      <c r="AB124" s="44"/>
       <c r="AC124" s="5"/>
     </row>
     <row r="125" spans="1:29">
@@ -13757,8 +13932,8 @@
       <c r="Z125" s="41">
         <v>0</v>
       </c>
-      <c r="AA125" s="43"/>
-      <c r="AB125" s="43"/>
+      <c r="AA125" s="44"/>
+      <c r="AB125" s="44"/>
       <c r="AC125" s="5"/>
     </row>
     <row r="126" spans="1:29">
@@ -13828,8 +14003,8 @@
       <c r="Z126" s="41">
         <v>0</v>
       </c>
-      <c r="AA126" s="43"/>
-      <c r="AB126" s="43"/>
+      <c r="AA126" s="44"/>
+      <c r="AB126" s="44"/>
       <c r="AC126" s="5"/>
     </row>
     <row r="127" spans="1:29">
@@ -13901,8 +14076,8 @@
       <c r="Z127" s="41">
         <v>0</v>
       </c>
-      <c r="AA127" s="43"/>
-      <c r="AB127" s="43"/>
+      <c r="AA127" s="44"/>
+      <c r="AB127" s="44"/>
       <c r="AC127" s="5"/>
     </row>
     <row r="128" spans="1:29">
@@ -13972,8 +14147,8 @@
       <c r="Z128" s="41">
         <v>0</v>
       </c>
-      <c r="AA128" s="43"/>
-      <c r="AB128" s="43"/>
+      <c r="AA128" s="44"/>
+      <c r="AB128" s="44"/>
       <c r="AC128" s="5"/>
     </row>
     <row r="129" spans="1:29">
@@ -14045,8 +14220,8 @@
       <c r="Z129" s="41">
         <v>0</v>
       </c>
-      <c r="AA129" s="43"/>
-      <c r="AB129" s="43"/>
+      <c r="AA129" s="44"/>
+      <c r="AB129" s="44"/>
       <c r="AC129" s="5"/>
     </row>
     <row r="130" spans="1:29">
@@ -14116,8 +14291,8 @@
       <c r="Z130" s="41">
         <v>0</v>
       </c>
-      <c r="AA130" s="43"/>
-      <c r="AB130" s="43"/>
+      <c r="AA130" s="44"/>
+      <c r="AB130" s="44"/>
       <c r="AC130" s="5"/>
     </row>
     <row r="131" spans="1:29">
@@ -14187,8 +14362,8 @@
       <c r="Z131" s="41">
         <v>0</v>
       </c>
-      <c r="AA131" s="43"/>
-      <c r="AB131" s="43"/>
+      <c r="AA131" s="44"/>
+      <c r="AB131" s="44"/>
       <c r="AC131" s="5"/>
     </row>
     <row r="132" spans="1:29">
@@ -14258,8 +14433,8 @@
       <c r="Z132" s="41">
         <v>0</v>
       </c>
-      <c r="AA132" s="43"/>
-      <c r="AB132" s="43"/>
+      <c r="AA132" s="44"/>
+      <c r="AB132" s="44"/>
       <c r="AC132" s="5"/>
     </row>
     <row r="133" spans="1:29">
@@ -14331,8 +14506,8 @@
       <c r="Z133" s="41">
         <v>0</v>
       </c>
-      <c r="AA133" s="43"/>
-      <c r="AB133" s="43"/>
+      <c r="AA133" s="44"/>
+      <c r="AB133" s="44"/>
       <c r="AC133" s="5"/>
     </row>
     <row r="134" spans="1:29">
@@ -14404,8 +14579,8 @@
       <c r="Z134" s="41">
         <v>0</v>
       </c>
-      <c r="AA134" s="43"/>
-      <c r="AB134" s="43"/>
+      <c r="AA134" s="44"/>
+      <c r="AB134" s="44"/>
       <c r="AC134" s="5"/>
     </row>
     <row r="135" spans="1:29">
@@ -14477,8 +14652,8 @@
       <c r="Z135" s="41">
         <v>0</v>
       </c>
-      <c r="AA135" s="43"/>
-      <c r="AB135" s="43"/>
+      <c r="AA135" s="44"/>
+      <c r="AB135" s="44"/>
       <c r="AC135" s="5"/>
     </row>
     <row r="136" spans="1:29">
@@ -14550,8 +14725,8 @@
       <c r="Z136" s="41">
         <v>0</v>
       </c>
-      <c r="AA136" s="43"/>
-      <c r="AB136" s="43"/>
+      <c r="AA136" s="44"/>
+      <c r="AB136" s="44"/>
       <c r="AC136" s="5"/>
     </row>
     <row r="137" spans="1:29">
@@ -14623,8 +14798,8 @@
       <c r="Z137" s="41">
         <v>0</v>
       </c>
-      <c r="AA137" s="43"/>
-      <c r="AB137" s="43"/>
+      <c r="AA137" s="44"/>
+      <c r="AB137" s="44"/>
       <c r="AC137" s="5"/>
     </row>
     <row r="138" spans="1:29">
@@ -14696,8 +14871,8 @@
       <c r="Z138" s="41">
         <v>0</v>
       </c>
-      <c r="AA138" s="43"/>
-      <c r="AB138" s="43"/>
+      <c r="AA138" s="44"/>
+      <c r="AB138" s="44"/>
       <c r="AC138" s="5"/>
     </row>
     <row r="139" spans="1:29">
@@ -14769,8 +14944,8 @@
       <c r="Z139" s="41">
         <v>0</v>
       </c>
-      <c r="AA139" s="43"/>
-      <c r="AB139" s="43"/>
+      <c r="AA139" s="44"/>
+      <c r="AB139" s="44"/>
       <c r="AC139" s="5"/>
     </row>
     <row r="140" spans="1:29">
@@ -14842,8 +15017,8 @@
       <c r="Z140" s="41">
         <v>0</v>
       </c>
-      <c r="AA140" s="43"/>
-      <c r="AB140" s="43"/>
+      <c r="AA140" s="44"/>
+      <c r="AB140" s="44"/>
       <c r="AC140" s="5"/>
     </row>
     <row r="141" spans="1:29">
@@ -14915,8 +15090,8 @@
       <c r="Z141" s="41">
         <v>0</v>
       </c>
-      <c r="AA141" s="43"/>
-      <c r="AB141" s="43"/>
+      <c r="AA141" s="44"/>
+      <c r="AB141" s="44"/>
       <c r="AC141" s="5"/>
     </row>
     <row r="142" spans="1:29">
@@ -14986,8 +15161,8 @@
       <c r="Z142" s="41">
         <v>0</v>
       </c>
-      <c r="AA142" s="43"/>
-      <c r="AB142" s="43"/>
+      <c r="AA142" s="44"/>
+      <c r="AB142" s="44"/>
       <c r="AC142" s="5"/>
     </row>
     <row r="143" spans="1:29">
@@ -15057,8 +15232,8 @@
       <c r="Z143" s="41">
         <v>0</v>
       </c>
-      <c r="AA143" s="43"/>
-      <c r="AB143" s="43"/>
+      <c r="AA143" s="44"/>
+      <c r="AB143" s="44"/>
       <c r="AC143" s="5"/>
     </row>
     <row r="144" spans="1:29">
@@ -15128,8 +15303,8 @@
       <c r="Z144" s="41">
         <v>0</v>
       </c>
-      <c r="AA144" s="43"/>
-      <c r="AB144" s="43"/>
+      <c r="AA144" s="44"/>
+      <c r="AB144" s="44"/>
       <c r="AC144" s="5"/>
     </row>
     <row r="145" spans="1:29">
@@ -15199,8 +15374,8 @@
       <c r="Z145" s="41">
         <v>0</v>
       </c>
-      <c r="AA145" s="43"/>
-      <c r="AB145" s="43"/>
+      <c r="AA145" s="44"/>
+      <c r="AB145" s="44"/>
       <c r="AC145" s="5"/>
     </row>
     <row r="146" spans="1:29">
@@ -15268,8 +15443,8 @@
       <c r="Z146" s="41">
         <v>0</v>
       </c>
-      <c r="AA146" s="43"/>
-      <c r="AB146" s="43"/>
+      <c r="AA146" s="44"/>
+      <c r="AB146" s="44"/>
       <c r="AC146" s="5"/>
     </row>
     <row r="147" spans="1:29">
@@ -15339,8 +15514,8 @@
       <c r="Z147" s="41">
         <v>0</v>
       </c>
-      <c r="AA147" s="43"/>
-      <c r="AB147" s="43"/>
+      <c r="AA147" s="44"/>
+      <c r="AB147" s="44"/>
       <c r="AC147" s="5"/>
     </row>
     <row r="148" spans="1:29">
@@ -15410,8 +15585,8 @@
       <c r="Z148" s="41">
         <v>0</v>
       </c>
-      <c r="AA148" s="43"/>
-      <c r="AB148" s="43"/>
+      <c r="AA148" s="44"/>
+      <c r="AB148" s="44"/>
       <c r="AC148" s="5"/>
     </row>
     <row r="149" spans="1:29">
@@ -15483,8 +15658,8 @@
       <c r="Z149" s="41">
         <v>0</v>
       </c>
-      <c r="AA149" s="43"/>
-      <c r="AB149" s="43"/>
+      <c r="AA149" s="44"/>
+      <c r="AB149" s="44"/>
       <c r="AC149" s="5"/>
     </row>
     <row r="150" spans="1:29" ht="28">
@@ -15552,8 +15727,8 @@
       <c r="Z150" s="41">
         <v>0</v>
       </c>
-      <c r="AA150" s="43"/>
-      <c r="AB150" s="43"/>
+      <c r="AA150" s="44"/>
+      <c r="AB150" s="44"/>
       <c r="AC150" s="5"/>
     </row>
     <row r="151" spans="1:29">
@@ -15623,8 +15798,8 @@
       <c r="Z151" s="41">
         <v>0</v>
       </c>
-      <c r="AA151" s="43"/>
-      <c r="AB151" s="43"/>
+      <c r="AA151" s="44"/>
+      <c r="AB151" s="44"/>
       <c r="AC151" s="5"/>
     </row>
     <row r="152" spans="1:29">
@@ -15694,8 +15869,8 @@
       <c r="Z152" s="41">
         <v>0</v>
       </c>
-      <c r="AA152" s="43"/>
-      <c r="AB152" s="43"/>
+      <c r="AA152" s="44"/>
+      <c r="AB152" s="44"/>
       <c r="AC152" s="5"/>
     </row>
     <row r="153" spans="1:29">
@@ -15763,8 +15938,8 @@
       <c r="Z153" s="41">
         <v>0</v>
       </c>
-      <c r="AA153" s="43"/>
-      <c r="AB153" s="43"/>
+      <c r="AA153" s="44"/>
+      <c r="AB153" s="44"/>
       <c r="AC153" s="5"/>
     </row>
     <row r="154" spans="1:29">
@@ -15834,8 +16009,8 @@
       <c r="Z154" s="41">
         <v>0</v>
       </c>
-      <c r="AA154" s="43"/>
-      <c r="AB154" s="43"/>
+      <c r="AA154" s="44"/>
+      <c r="AB154" s="44"/>
       <c r="AC154" s="5"/>
     </row>
     <row r="155" spans="1:29">
@@ -15905,8 +16080,8 @@
       <c r="Z155" s="41">
         <v>0</v>
       </c>
-      <c r="AA155" s="43"/>
-      <c r="AB155" s="43"/>
+      <c r="AA155" s="44"/>
+      <c r="AB155" s="44"/>
       <c r="AC155" s="5"/>
     </row>
     <row r="156" spans="1:29">
@@ -15976,8 +16151,8 @@
       <c r="Z156" s="41">
         <v>0</v>
       </c>
-      <c r="AA156" s="43"/>
-      <c r="AB156" s="43"/>
+      <c r="AA156" s="44"/>
+      <c r="AB156" s="44"/>
       <c r="AC156" s="5"/>
     </row>
     <row r="157" spans="1:29">
@@ -16049,8 +16224,8 @@
       <c r="Z157" s="41">
         <v>0</v>
       </c>
-      <c r="AA157" s="43"/>
-      <c r="AB157" s="43"/>
+      <c r="AA157" s="44"/>
+      <c r="AB157" s="44"/>
       <c r="AC157" s="5"/>
     </row>
     <row r="158" spans="1:29" ht="28">
@@ -16118,8 +16293,8 @@
       <c r="Z158" s="41">
         <v>0</v>
       </c>
-      <c r="AA158" s="43"/>
-      <c r="AB158" s="43"/>
+      <c r="AA158" s="44"/>
+      <c r="AB158" s="44"/>
       <c r="AC158" s="5"/>
     </row>
     <row r="159" spans="1:29" ht="28">
@@ -16187,8 +16362,8 @@
       <c r="Z159" s="41">
         <v>0</v>
       </c>
-      <c r="AA159" s="43"/>
-      <c r="AB159" s="43"/>
+      <c r="AA159" s="44"/>
+      <c r="AB159" s="44"/>
       <c r="AC159" s="5"/>
     </row>
     <row r="160" spans="1:29">
@@ -16258,8 +16433,8 @@
       <c r="Z160" s="41">
         <v>0</v>
       </c>
-      <c r="AA160" s="43"/>
-      <c r="AB160" s="43"/>
+      <c r="AA160" s="44"/>
+      <c r="AB160" s="44"/>
       <c r="AC160" s="5"/>
     </row>
     <row r="161" spans="1:29">
@@ -16331,8 +16506,8 @@
       <c r="Z161" s="41">
         <v>0</v>
       </c>
-      <c r="AA161" s="43"/>
-      <c r="AB161" s="43"/>
+      <c r="AA161" s="44"/>
+      <c r="AB161" s="44"/>
       <c r="AC161" s="5"/>
     </row>
     <row r="162" spans="1:29">
@@ -16402,8 +16577,8 @@
       <c r="Z162" s="41">
         <v>0</v>
       </c>
-      <c r="AA162" s="43"/>
-      <c r="AB162" s="43"/>
+      <c r="AA162" s="44"/>
+      <c r="AB162" s="44"/>
       <c r="AC162" s="5"/>
     </row>
     <row r="163" spans="1:29">
@@ -16473,8 +16648,8 @@
       <c r="Z163" s="41">
         <v>0</v>
       </c>
-      <c r="AA163" s="43"/>
-      <c r="AB163" s="43"/>
+      <c r="AA163" s="44"/>
+      <c r="AB163" s="44"/>
       <c r="AC163" s="5"/>
     </row>
     <row r="164" spans="1:29">
@@ -16544,8 +16719,8 @@
       <c r="Z164" s="41">
         <v>0</v>
       </c>
-      <c r="AA164" s="43"/>
-      <c r="AB164" s="43"/>
+      <c r="AA164" s="44"/>
+      <c r="AB164" s="44"/>
       <c r="AC164" s="5"/>
     </row>
     <row r="165" spans="1:29">
@@ -16615,8 +16790,8 @@
       <c r="Z165" s="41">
         <v>0</v>
       </c>
-      <c r="AA165" s="43"/>
-      <c r="AB165" s="43"/>
+      <c r="AA165" s="44"/>
+      <c r="AB165" s="44"/>
       <c r="AC165" s="5"/>
     </row>
     <row r="166" spans="1:29">
@@ -16688,8 +16863,8 @@
       <c r="Z166" s="41">
         <v>0</v>
       </c>
-      <c r="AA166" s="43"/>
-      <c r="AB166" s="43"/>
+      <c r="AA166" s="44"/>
+      <c r="AB166" s="44"/>
       <c r="AC166" s="5"/>
     </row>
     <row r="167" spans="1:29">
@@ -16782,7 +16957,7 @@
     <dataValidation type="list" sqref="H2:H167" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Baru,Preloved"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Y2:Y167 U2:V167" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" sqref="U2:V167 Y2:Y167" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Ya,Tidak"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="W2:W167" xr:uid="{00000000-0002-0000-0000-000005000000}">
